--- a/bancos/manual/desc_classificacao_receita.xlsx
+++ b/bancos/manual/desc_classificacao_receita.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3974"/>
+  <dimension ref="A1:C3975"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -16609,7 +16609,7 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>1321500000000</t>
+          <t>1321500100000</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
@@ -16626,7 +16626,7 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>1321500000000</t>
+          <t>1321500101000</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
@@ -62135,12 +62135,12 @@
     <row r="3635">
       <c r="A3635" t="inlineStr">
         <is>
-          <t>2999990199000</t>
+          <t>2999990106000</t>
         </is>
       </c>
       <c r="B3635" t="inlineStr">
         <is>
-          <t>Demais Rec. Capital - Princ. - Demais</t>
+          <t>Demais Rec. Capital - Princ. - Rompimento da Barragem de Fundão em Mariana - Recursos Depositados no BDMG</t>
         </is>
       </c>
       <c r="C3635" t="inlineStr">
@@ -62152,131 +62152,131 @@
     <row r="3636">
       <c r="A3636" t="inlineStr">
         <is>
-          <t>2999990200000</t>
+          <t>2999990199000</t>
         </is>
       </c>
       <c r="B3636" t="inlineStr">
         <is>
-          <t>Demais Rec. Capital - Multas e Juros de Mora</t>
+          <t>Demais Rec. Capital - Princ. - Demais</t>
         </is>
       </c>
       <c r="C3636" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3637">
       <c r="A3637" t="inlineStr">
         <is>
-          <t>2999990203000</t>
+          <t>2999990200000</t>
         </is>
       </c>
       <c r="B3637" t="inlineStr">
         <is>
-          <t>Demais Rec. Capital - MJM - Rompimento da Barragem de Fundão em Mariana - Renova</t>
+          <t>Demais Rec. Capital - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3637" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3638">
       <c r="A3638" t="inlineStr">
         <is>
-          <t>2999990300000</t>
+          <t>2999990203000</t>
         </is>
       </c>
       <c r="B3638" t="inlineStr">
         <is>
-          <t>Demais Rec. Capital - Dívida Ativa</t>
+          <t>Demais Rec. Capital - MJM - Rompimento da Barragem de Fundão em Mariana - Renova</t>
         </is>
       </c>
       <c r="C3638" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3639">
       <c r="A3639" t="inlineStr">
         <is>
-          <t>2999990303000</t>
+          <t>2999990300000</t>
         </is>
       </c>
       <c r="B3639" t="inlineStr">
         <is>
-          <t>Demais Rec. Capital - DA - Rompimento da Barragem de Fundão em Mariana - Renova</t>
+          <t>Demais Rec. Capital - Dívida Ativa</t>
         </is>
       </c>
       <c r="C3639" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3640">
       <c r="A3640" t="inlineStr">
         <is>
-          <t>2999990400000</t>
+          <t>2999990303000</t>
         </is>
       </c>
       <c r="B3640" t="inlineStr">
         <is>
-          <t>Demais Rec. Capital - Dívida Ativa - Multas e Juros de Mora</t>
+          <t>Demais Rec. Capital - DA - Rompimento da Barragem de Fundão em Mariana - Renova</t>
         </is>
       </c>
       <c r="C3640" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3641">
       <c r="A3641" t="inlineStr">
         <is>
-          <t>2999990403000</t>
+          <t>2999990400000</t>
         </is>
       </c>
       <c r="B3641" t="inlineStr">
         <is>
-          <t>Demais Rec. Capital - DA-MJM - Rompimento da Barragem de Fundão em Mariana - Renova</t>
+          <t>Demais Rec. Capital - Dívida Ativa - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3641" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3642">
       <c r="A3642" t="inlineStr">
         <is>
-          <t>7000000000000</t>
+          <t>2999990403000</t>
         </is>
       </c>
       <c r="B3642" t="inlineStr">
         <is>
-          <t>Receita Intraorçamentária</t>
+          <t>Demais Rec. Capital - DA-MJM - Rompimento da Barragem de Fundão em Mariana - Renova</t>
         </is>
       </c>
       <c r="C3642" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3643">
       <c r="A3643" t="inlineStr">
         <is>
-          <t>7100000000000</t>
+          <t>7000000000000</t>
         </is>
       </c>
       <c r="B3643" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Impostos, Taxas e Contribuições de Melhoria</t>
+          <t>Receita Intraorçamentária</t>
         </is>
       </c>
       <c r="C3643" t="inlineStr">
@@ -62288,12 +62288,12 @@
     <row r="3644">
       <c r="A3644" t="inlineStr">
         <is>
-          <t>7120000000000</t>
+          <t>7100000000000</t>
         </is>
       </c>
       <c r="B3644" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Taxas</t>
+          <t>Rec. Intra. - Impostos, Taxas e Contribuições de Melhoria</t>
         </is>
       </c>
       <c r="C3644" t="inlineStr">
@@ -62305,12 +62305,12 @@
     <row r="3645">
       <c r="A3645" t="inlineStr">
         <is>
-          <t>7121000000000</t>
+          <t>7120000000000</t>
         </is>
       </c>
       <c r="B3645" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Taxas pelo Exercício do Poder de Polícia</t>
+          <t>Rec. Intra. - Taxas</t>
         </is>
       </c>
       <c r="C3645" t="inlineStr">
@@ -62322,12 +62322,12 @@
     <row r="3646">
       <c r="A3646" t="inlineStr">
         <is>
-          <t>7121010000000</t>
+          <t>7121000000000</t>
         </is>
       </c>
       <c r="B3646" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Taxas de Inspeção, Controle e Fiscalização</t>
+          <t>Rec. Intra. - Taxas pelo Exercício do Poder de Polícia</t>
         </is>
       </c>
       <c r="C3646" t="inlineStr">
@@ -62339,12 +62339,12 @@
     <row r="3647">
       <c r="A3647" t="inlineStr">
         <is>
-          <t>7121010100000</t>
+          <t>7121010000000</t>
         </is>
       </c>
       <c r="B3647" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Tx. Insp. Contr. Fisc. - Principal</t>
+          <t>Rec. Intra. - Taxas de Inspeção, Controle e Fiscalização</t>
         </is>
       </c>
       <c r="C3647" t="inlineStr">
@@ -62356,12 +62356,12 @@
     <row r="3648">
       <c r="A3648" t="inlineStr">
         <is>
-          <t>7121010101000</t>
+          <t>7121010100000</t>
         </is>
       </c>
       <c r="B3648" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Tx. Insp. Contr. Fisc. - Princ. - Taxa de Segurança Pública</t>
+          <t>Rec. Intra. - Tx. Insp. Contr. Fisc. - Principal</t>
         </is>
       </c>
       <c r="C3648" t="inlineStr">
@@ -62373,46 +62373,46 @@
     <row r="3649">
       <c r="A3649" t="inlineStr">
         <is>
-          <t>7121010101005</t>
+          <t>7121010101000</t>
         </is>
       </c>
       <c r="B3649" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Tx. Insp. Contr. Fisc. - Princ. - Tx. Segurança Pública - Taxa de Incêndio - Corpo de Bombeiros Militar do Estado de Minas Gerais - CBMMG</t>
+          <t>Rec. Intra. - Tx. Insp. Contr. Fisc. - Princ. - Taxa de Segurança Pública</t>
         </is>
       </c>
       <c r="C3649" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3650">
       <c r="A3650" t="inlineStr">
         <is>
-          <t>7121040000000</t>
+          <t>7121010101005</t>
         </is>
       </c>
       <c r="B3650" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Taxa de Controle e Fiscalização Ambiental</t>
+          <t>Rec. Intra. - Tx. Insp. Contr. Fisc. - Princ. - Tx. Segurança Pública - Taxa de Incêndio - Corpo de Bombeiros Militar do Estado de Minas Gerais - CBMMG</t>
         </is>
       </c>
       <c r="C3650" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3651">
       <c r="A3651" t="inlineStr">
         <is>
-          <t>7121040100000</t>
+          <t>7121040000000</t>
         </is>
       </c>
       <c r="B3651" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Tx. Contr. Fisc. Ambient. - Principal</t>
+          <t>Rec. Intra. - Taxa de Controle e Fiscalização Ambiental</t>
         </is>
       </c>
       <c r="C3651" t="inlineStr">
@@ -62424,29 +62424,29 @@
     <row r="3652">
       <c r="A3652" t="inlineStr">
         <is>
-          <t>7121040103000</t>
+          <t>7121040100000</t>
         </is>
       </c>
       <c r="B3652" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Tx. Contr. Fisc. Ambient. - Princ. - Taxa de Controle e Fiscalização Ambiental</t>
+          <t>Rec. Intra. - Tx. Contr. Fisc. Ambient. - Principal</t>
         </is>
       </c>
       <c r="C3652" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3653">
       <c r="A3653" t="inlineStr">
         <is>
-          <t>7121040104000</t>
+          <t>7121040103000</t>
         </is>
       </c>
       <c r="B3653" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Tx. Contr. Fisc. Ambient. - Princ. - Taxa de Regularização Ambiental</t>
+          <t>Rec. Intra. - Tx. Contr. Fisc. Ambient. - Princ. - Taxa de Controle e Fiscalização Ambiental</t>
         </is>
       </c>
       <c r="C3653" t="inlineStr">
@@ -62458,29 +62458,29 @@
     <row r="3654">
       <c r="A3654" t="inlineStr">
         <is>
-          <t>7200000000000</t>
+          <t>7121040104000</t>
         </is>
       </c>
       <c r="B3654" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contribuições</t>
+          <t>Rec. Intra. - Tx. Contr. Fisc. Ambient. - Princ. - Taxa de Regularização Ambiental</t>
         </is>
       </c>
       <c r="C3654" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3655">
       <c r="A3655" t="inlineStr">
         <is>
-          <t>7210000000000</t>
+          <t>7200000000000</t>
         </is>
       </c>
       <c r="B3655" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contribuições Sociais</t>
+          <t>Rec. Intra. - Contribuições</t>
         </is>
       </c>
       <c r="C3655" t="inlineStr">
@@ -62492,12 +62492,12 @@
     <row r="3656">
       <c r="A3656" t="inlineStr">
         <is>
-          <t>7215000000000</t>
+          <t>7210000000000</t>
         </is>
       </c>
       <c r="B3656" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contribuições para Regimes Próprios de Previdência e Sistema de Proteção Social</t>
+          <t>Rec. Intra. - Contribuições Sociais</t>
         </is>
       </c>
       <c r="C3656" t="inlineStr">
@@ -62509,12 +62509,12 @@
     <row r="3657">
       <c r="A3657" t="inlineStr">
         <is>
-          <t>7215020000000</t>
+          <t>7215000000000</t>
         </is>
       </c>
       <c r="B3657" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contribuição Patronal - Servidor Civil</t>
+          <t>Rec. Intra. - Contribuições para Regimes Próprios de Previdência e Sistema de Proteção Social</t>
         </is>
       </c>
       <c r="C3657" t="inlineStr">
@@ -62526,12 +62526,12 @@
     <row r="3658">
       <c r="A3658" t="inlineStr">
         <is>
-          <t>7215021000000</t>
+          <t>7215020000000</t>
         </is>
       </c>
       <c r="B3658" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contribuição Patronal - Servidor Civil Ativo</t>
+          <t>Rec. Intra. - Contribuição Patronal - Servidor Civil</t>
         </is>
       </c>
       <c r="C3658" t="inlineStr">
@@ -62543,12 +62543,12 @@
     <row r="3659">
       <c r="A3659" t="inlineStr">
         <is>
-          <t>7215021100000</t>
+          <t>7215021000000</t>
         </is>
       </c>
       <c r="B3659" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Principal</t>
+          <t>Rec. Intra. - Contribuição Patronal - Servidor Civil Ativo</t>
         </is>
       </c>
       <c r="C3659" t="inlineStr">
@@ -62560,12 +62560,12 @@
     <row r="3660">
       <c r="A3660" t="inlineStr">
         <is>
-          <t>7215021101000</t>
+          <t>7215021100000</t>
         </is>
       </c>
       <c r="B3660" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Poder Executivo</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Principal</t>
         </is>
       </c>
       <c r="C3660" t="inlineStr">
@@ -62577,29 +62577,29 @@
     <row r="3661">
       <c r="A3661" t="inlineStr">
         <is>
-          <t>7215021101001</t>
+          <t>7215021101000</t>
         </is>
       </c>
       <c r="B3661" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Executivo - Contrib. Ordinária</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Poder Executivo</t>
         </is>
       </c>
       <c r="C3661" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3662">
       <c r="A3662" t="inlineStr">
         <is>
-          <t>7215021101002</t>
+          <t>7215021101001</t>
         </is>
       </c>
       <c r="B3662" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Executivo - Contrib. Suplementar</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Executivo - Contrib. Ordinária</t>
         </is>
       </c>
       <c r="C3662" t="inlineStr">
@@ -62611,267 +62611,267 @@
     <row r="3663">
       <c r="A3663" t="inlineStr">
         <is>
-          <t>7215021102000</t>
+          <t>7215021101002</t>
         </is>
       </c>
       <c r="B3663" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Assembleia Legislativa do Estado de Minas Gerais - ALMG</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Executivo - Contrib. Suplementar</t>
         </is>
       </c>
       <c r="C3663" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3664">
       <c r="A3664" t="inlineStr">
         <is>
-          <t>7215021102001</t>
+          <t>7215021102000</t>
         </is>
       </c>
       <c r="B3664" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - ALMG - Contrib. Ordinária</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Assembleia Legislativa do Estado de Minas Gerais - ALMG</t>
         </is>
       </c>
       <c r="C3664" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3665">
       <c r="A3665" t="inlineStr">
         <is>
-          <t>7215021103000</t>
+          <t>7215021102001</t>
         </is>
       </c>
       <c r="B3665" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Tribunal de Contas do Estado de Minas Gerais - TCEMG</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - ALMG - Contrib. Ordinária</t>
         </is>
       </c>
       <c r="C3665" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3666">
       <c r="A3666" t="inlineStr">
         <is>
-          <t>7215021103001</t>
+          <t>7215021103000</t>
         </is>
       </c>
       <c r="B3666" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - TCEMG - Contrib. Ordinária</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Tribunal de Contas do Estado de Minas Gerais - TCEMG</t>
         </is>
       </c>
       <c r="C3666" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3667">
       <c r="A3667" t="inlineStr">
         <is>
-          <t>7215021104000</t>
+          <t>7215021103001</t>
         </is>
       </c>
       <c r="B3667" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Tribunal de Justiça do Estado de Minas Gerais - TJMG</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - TCEMG - Contrib. Ordinária</t>
         </is>
       </c>
       <c r="C3667" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3668">
       <c r="A3668" t="inlineStr">
         <is>
-          <t>7215021104001</t>
+          <t>7215021104000</t>
         </is>
       </c>
       <c r="B3668" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - TJMG - Contrib. Ordinária</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Tribunal de Justiça do Estado de Minas Gerais - TJMG</t>
         </is>
       </c>
       <c r="C3668" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3669">
       <c r="A3669" t="inlineStr">
         <is>
-          <t>7215021105000</t>
+          <t>7215021104001</t>
         </is>
       </c>
       <c r="B3669" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Tribunal de Justiça Militar do Estado de Minas Gerais - TJMMG</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - TJMG - Contrib. Ordinária</t>
         </is>
       </c>
       <c r="C3669" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3670">
       <c r="A3670" t="inlineStr">
         <is>
-          <t>7215021105001</t>
+          <t>7215021105000</t>
         </is>
       </c>
       <c r="B3670" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - TJMMG - Contrib. Ordinária</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Tribunal de Justiça Militar do Estado de Minas Gerais - TJMMG</t>
         </is>
       </c>
       <c r="C3670" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3671">
       <c r="A3671" t="inlineStr">
         <is>
-          <t>7215021106000</t>
+          <t>7215021105001</t>
         </is>
       </c>
       <c r="B3671" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Ministério Público do Estado de Minas Gerais - MPMG</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - TJMMG - Contrib. Ordinária</t>
         </is>
       </c>
       <c r="C3671" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3672">
       <c r="A3672" t="inlineStr">
         <is>
-          <t>7215021106001</t>
+          <t>7215021106000</t>
         </is>
       </c>
       <c r="B3672" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - MPMG - Contrib. Ordinária</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Ministério Público do Estado de Minas Gerais - MPMG</t>
         </is>
       </c>
       <c r="C3672" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3673">
       <c r="A3673" t="inlineStr">
         <is>
-          <t>7215021107000</t>
+          <t>7215021106001</t>
         </is>
       </c>
       <c r="B3673" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Defensoria Pública do Estado de Minas Gerais - DEFPUB</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - MPMG - Contrib. Ordinária</t>
         </is>
       </c>
       <c r="C3673" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3674">
       <c r="A3674" t="inlineStr">
         <is>
-          <t>7215021107001</t>
+          <t>7215021107000</t>
         </is>
       </c>
       <c r="B3674" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - DEFPUB - Contrib. Ordinária</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Defensoria Pública do Estado de Minas Gerais - DEFPUB</t>
         </is>
       </c>
       <c r="C3674" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3675">
       <c r="A3675" t="inlineStr">
         <is>
-          <t>7215021199000</t>
+          <t>7215021107001</t>
         </is>
       </c>
       <c r="B3675" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Demais</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - DEFPUB - Contrib. Ordinária</t>
         </is>
       </c>
       <c r="C3675" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3676">
       <c r="A3676" t="inlineStr">
         <is>
-          <t>7215021199002</t>
+          <t>7215021199000</t>
         </is>
       </c>
       <c r="B3676" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Demais - Municípios</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Demais</t>
         </is>
       </c>
       <c r="C3676" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3677">
       <c r="A3677" t="inlineStr">
         <is>
-          <t>7215530000000</t>
+          <t>7215021199002</t>
         </is>
       </c>
       <c r="B3677" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contribuição Patronal para o Sistema de Proteção Social dos Militares</t>
+          <t>Rec. Intra. - Contrib. Patron. - Serv. Civil Ativo - Princ. - Demais - Municípios</t>
         </is>
       </c>
       <c r="C3677" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3678">
       <c r="A3678" t="inlineStr">
         <is>
-          <t>7215531000000</t>
+          <t>7215530000000</t>
         </is>
       </c>
       <c r="B3678" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contribuição Patronal - Militar Ativo</t>
+          <t>Rec. Intra. - Contribuição Patronal para o Sistema de Proteção Social dos Militares</t>
         </is>
       </c>
       <c r="C3678" t="inlineStr">
@@ -62883,12 +62883,12 @@
     <row r="3679">
       <c r="A3679" t="inlineStr">
         <is>
-          <t>7215531100000</t>
+          <t>7215531000000</t>
         </is>
       </c>
       <c r="B3679" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patronal - Militar Ativo - Principal</t>
+          <t>Rec. Intra. - Contribuição Patronal - Militar Ativo</t>
         </is>
       </c>
       <c r="C3679" t="inlineStr">
@@ -62900,29 +62900,29 @@
     <row r="3680">
       <c r="A3680" t="inlineStr">
         <is>
-          <t>7215531101000</t>
+          <t>7215531100000</t>
         </is>
       </c>
       <c r="B3680" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Militar Ativo - Princ. - Saúde</t>
+          <t>Rec. Intra. - Contrib. Patronal - Militar Ativo - Principal</t>
         </is>
       </c>
       <c r="C3680" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3681">
       <c r="A3681" t="inlineStr">
         <is>
-          <t>7215531102000</t>
+          <t>7215531101000</t>
         </is>
       </c>
       <c r="B3681" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Militar Ativo - Princ. - Pensão</t>
+          <t>Rec. Intra. - Contrib. Patron. - Militar Ativo - Princ. - Saúde</t>
         </is>
       </c>
       <c r="C3681" t="inlineStr">
@@ -62934,12 +62934,12 @@
     <row r="3682">
       <c r="A3682" t="inlineStr">
         <is>
-          <t>7215531103000</t>
+          <t>7215531102000</t>
         </is>
       </c>
       <c r="B3682" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patron. - Militar Ativo - Princ. - Aposentadoria</t>
+          <t>Rec. Intra. - Contrib. Patron. - Militar Ativo - Princ. - Pensão</t>
         </is>
       </c>
       <c r="C3682" t="inlineStr">
@@ -62951,29 +62951,29 @@
     <row r="3683">
       <c r="A3683" t="inlineStr">
         <is>
-          <t>7215532000000</t>
+          <t>7215531103000</t>
         </is>
       </c>
       <c r="B3683" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contribuição Patronal do Militar Inativo</t>
+          <t>Rec. Intra. - Contrib. Patron. - Militar Ativo - Princ. - Aposentadoria</t>
         </is>
       </c>
       <c r="C3683" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3684">
       <c r="A3684" t="inlineStr">
         <is>
-          <t>7215532100000</t>
+          <t>7215532000000</t>
         </is>
       </c>
       <c r="B3684" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patronal Militar Inativo - Principal</t>
+          <t>Rec. Intra. - Contribuição Patronal do Militar Inativo</t>
         </is>
       </c>
       <c r="C3684" t="inlineStr">
@@ -62985,29 +62985,29 @@
     <row r="3685">
       <c r="A3685" t="inlineStr">
         <is>
-          <t>7215532101000</t>
+          <t>7215532100000</t>
         </is>
       </c>
       <c r="B3685" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patronal Militar Inativo - Princ. - Saúde</t>
+          <t>Rec. Intra. - Contrib. Patronal Militar Inativo - Principal</t>
         </is>
       </c>
       <c r="C3685" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3686">
       <c r="A3686" t="inlineStr">
         <is>
-          <t>7215532102000</t>
+          <t>7215532101000</t>
         </is>
       </c>
       <c r="B3686" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patronal Militar Inativo - Princ. - Pensão</t>
+          <t>Rec. Intra. - Contrib. Patronal Militar Inativo - Princ. - Saúde</t>
         </is>
       </c>
       <c r="C3686" t="inlineStr">
@@ -63019,12 +63019,12 @@
     <row r="3687">
       <c r="A3687" t="inlineStr">
         <is>
-          <t>7215532103000</t>
+          <t>7215532102000</t>
         </is>
       </c>
       <c r="B3687" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Contrib. Patronal Militar Inativo - Princ. - Aposentadoria</t>
+          <t>Rec. Intra. - Contrib. Patronal Militar Inativo - Princ. - Pensão</t>
         </is>
       </c>
       <c r="C3687" t="inlineStr">
@@ -63036,29 +63036,29 @@
     <row r="3688">
       <c r="A3688" t="inlineStr">
         <is>
-          <t>7219000000000</t>
+          <t>7215532103000</t>
         </is>
       </c>
       <c r="B3688" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Contribuições Sociais</t>
+          <t>Rec. Intra. - Contrib. Patronal Militar Inativo - Princ. - Aposentadoria</t>
         </is>
       </c>
       <c r="C3688" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3689">
       <c r="A3689" t="inlineStr">
         <is>
-          <t>7219990000000</t>
+          <t>7219000000000</t>
         </is>
       </c>
       <c r="B3689" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contribuições Sociais</t>
+          <t>Rec. Intra. - Outras Contribuições Sociais</t>
         </is>
       </c>
       <c r="C3689" t="inlineStr">
@@ -63070,12 +63070,12 @@
     <row r="3690">
       <c r="A3690" t="inlineStr">
         <is>
-          <t>7219991000000</t>
+          <t>7219990000000</t>
         </is>
       </c>
       <c r="B3690" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contribuições Sociais não Arrecadadas e não Projetadas pela RFB</t>
+          <t>Rec. Intra. - Demais Contribuições Sociais</t>
         </is>
       </c>
       <c r="C3690" t="inlineStr">
@@ -63087,12 +63087,12 @@
     <row r="3691">
       <c r="A3691" t="inlineStr">
         <is>
-          <t>7219991100000</t>
+          <t>7219991000000</t>
         </is>
       </c>
       <c r="B3691" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Principal</t>
+          <t>Rec. Intra. - Demais Contribuições Sociais não Arrecadadas e não Projetadas pela RFB</t>
         </is>
       </c>
       <c r="C3691" t="inlineStr">
@@ -63104,12 +63104,12 @@
     <row r="3692">
       <c r="A3692" t="inlineStr">
         <is>
-          <t>7219991101000</t>
+          <t>7219991100000</t>
         </is>
       </c>
       <c r="B3692" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patronal do Civil para a Saúde</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Principal</t>
         </is>
       </c>
       <c r="C3692" t="inlineStr">
@@ -63121,29 +63121,29 @@
     <row r="3693">
       <c r="A3693" t="inlineStr">
         <is>
-          <t>7219991101001</t>
+          <t>7219991101000</t>
         </is>
       </c>
       <c r="B3693" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Servidor Ativo</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patronal do Civil para a Saúde</t>
         </is>
       </c>
       <c r="C3693" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3694">
       <c r="A3694" t="inlineStr">
         <is>
-          <t>7219991101002</t>
+          <t>7219991101001</t>
         </is>
       </c>
       <c r="B3694" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Servidor Inativo</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Servidor Ativo</t>
         </is>
       </c>
       <c r="C3694" t="inlineStr">
@@ -63155,12 +63155,12 @@
     <row r="3695">
       <c r="A3695" t="inlineStr">
         <is>
-          <t>7219991101003</t>
+          <t>7219991101002</t>
         </is>
       </c>
       <c r="B3695" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Pensionista</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Servidor Inativo</t>
         </is>
       </c>
       <c r="C3695" t="inlineStr">
@@ -63172,12 +63172,12 @@
     <row r="3696">
       <c r="A3696" t="inlineStr">
         <is>
-          <t>7219991101004</t>
+          <t>7219991101003</t>
         </is>
       </c>
       <c r="B3696" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Contrato Administrativo</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Pensionista</t>
         </is>
       </c>
       <c r="C3696" t="inlineStr">
@@ -63189,12 +63189,12 @@
     <row r="3697">
       <c r="A3697" t="inlineStr">
         <is>
-          <t>7219991101005</t>
+          <t>7219991101004</t>
         </is>
       </c>
       <c r="B3697" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Estado - Dependentes</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Contrato Administrativo</t>
         </is>
       </c>
       <c r="C3697" t="inlineStr">
@@ -63206,12 +63206,12 @@
     <row r="3698">
       <c r="A3698" t="inlineStr">
         <is>
-          <t>7219991101006</t>
+          <t>7219991101005</t>
         </is>
       </c>
       <c r="B3698" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Estado - Dependentes - Filhos</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Estado - Dependentes</t>
         </is>
       </c>
       <c r="C3698" t="inlineStr">
@@ -63223,12 +63223,12 @@
     <row r="3699">
       <c r="A3699" t="inlineStr">
         <is>
-          <t>7219991101007</t>
+          <t>7219991101006</t>
         </is>
       </c>
       <c r="B3699" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Usuário Facultativo</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Estado - Dependentes - Filhos</t>
         </is>
       </c>
       <c r="C3699" t="inlineStr">
@@ -63240,46 +63240,46 @@
     <row r="3700">
       <c r="A3700" t="inlineStr">
         <is>
-          <t>7219991103000</t>
+          <t>7219991101007</t>
         </is>
       </c>
       <c r="B3700" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Instituto de Previdência do Servidor Militar - IPSM</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patron. Civil Saúde - Usuário Facultativo</t>
         </is>
       </c>
       <c r="C3700" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3701">
       <c r="A3701" t="inlineStr">
         <is>
-          <t>7219991103051</t>
+          <t>7219991103000</t>
         </is>
       </c>
       <c r="B3701" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPSM - Contrib. Patronal - Ativo Civil</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Instituto de Previdência do Servidor Militar - IPSM</t>
         </is>
       </c>
       <c r="C3701" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3702">
       <c r="A3702" t="inlineStr">
         <is>
-          <t>7219991103052</t>
+          <t>7219991103051</t>
         </is>
       </c>
       <c r="B3702" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPSM - Contrib. Patronal - Inativo Civil</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPSM - Contrib. Patronal - Ativo Civil</t>
         </is>
       </c>
       <c r="C3702" t="inlineStr">
@@ -63291,12 +63291,12 @@
     <row r="3703">
       <c r="A3703" t="inlineStr">
         <is>
-          <t>7219991103053</t>
+          <t>7219991103052</t>
         </is>
       </c>
       <c r="B3703" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPSM - Contrib. Patronal Militar para a Saúde - Ativo</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPSM - Contrib. Patronal - Inativo Civil</t>
         </is>
       </c>
       <c r="C3703" t="inlineStr">
@@ -63308,12 +63308,12 @@
     <row r="3704">
       <c r="A3704" t="inlineStr">
         <is>
-          <t>7219991103054</t>
+          <t>7219991103053</t>
         </is>
       </c>
       <c r="B3704" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPSM - Contrib. Patronal Militar para a Saúde - Inativo</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPSM - Contrib. Patronal Militar para a Saúde - Ativo</t>
         </is>
       </c>
       <c r="C3704" t="inlineStr">
@@ -63325,12 +63325,12 @@
     <row r="3705">
       <c r="A3705" t="inlineStr">
         <is>
-          <t>7219991103055</t>
+          <t>7219991103054</t>
         </is>
       </c>
       <c r="B3705" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPSM - Contrib. Patronal Militar para a Previdência - Ativo</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPSM - Contrib. Patronal Militar para a Saúde - Inativo</t>
         </is>
       </c>
       <c r="C3705" t="inlineStr">
@@ -63342,12 +63342,12 @@
     <row r="3706">
       <c r="A3706" t="inlineStr">
         <is>
-          <t>7219991103056</t>
+          <t>7219991103055</t>
         </is>
       </c>
       <c r="B3706" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPSM - Contrib. Patronal Militar para a Previdência - Inativo</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPSM - Contrib. Patronal Militar para a Previdência - Ativo</t>
         </is>
       </c>
       <c r="C3706" t="inlineStr">
@@ -63359,80 +63359,80 @@
     <row r="3707">
       <c r="A3707" t="inlineStr">
         <is>
-          <t>7219991104000</t>
+          <t>7219991103056</t>
         </is>
       </c>
       <c r="B3707" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Instituto de Previdência do Legislativo do Estado de Minas Gerais - IPLEMG</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPSM - Contrib. Patronal Militar para a Previdência - Inativo</t>
         </is>
       </c>
       <c r="C3707" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3708">
       <c r="A3708" t="inlineStr">
         <is>
-          <t>7219991104051</t>
+          <t>7219991104000</t>
         </is>
       </c>
       <c r="B3708" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPLEMG - Contrib. Patronal - Exercente de Mandato Estadual</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Instituto de Previdência do Legislativo do Estado de Minas Gerais - IPLEMG</t>
         </is>
       </c>
       <c r="C3708" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3709">
       <c r="A3709" t="inlineStr">
         <is>
-          <t>7219991110000</t>
+          <t>7219991104051</t>
         </is>
       </c>
       <c r="B3709" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contribuição Patronal Militar para a Aposentadoria</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - IPLEMG - Contrib. Patronal - Exercente de Mandato Estadual</t>
         </is>
       </c>
       <c r="C3709" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3710">
       <c r="A3710" t="inlineStr">
         <is>
-          <t>7219991110051</t>
+          <t>7219991110000</t>
         </is>
       </c>
       <c r="B3710" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patronal Militar Aposentadoria - Ativo</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contribuição Patronal Militar para a Aposentadoria</t>
         </is>
       </c>
       <c r="C3710" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3711">
       <c r="A3711" t="inlineStr">
         <is>
-          <t>7219991110052</t>
+          <t>7219991110051</t>
         </is>
       </c>
       <c r="B3711" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patronal Militar Aposentadoria - Inativo</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patronal Militar Aposentadoria - Ativo</t>
         </is>
       </c>
       <c r="C3711" t="inlineStr">
@@ -63444,63 +63444,63 @@
     <row r="3712">
       <c r="A3712" t="inlineStr">
         <is>
-          <t>7219991200000</t>
+          <t>7219991110052</t>
         </is>
       </c>
       <c r="B3712" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - Multas e Juros de Mora</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Princ. - Contrib. Patronal Militar Aposentadoria - Inativo</t>
         </is>
       </c>
       <c r="C3712" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3713">
       <c r="A3713" t="inlineStr">
         <is>
-          <t>7219991205000</t>
+          <t>7219991200000</t>
         </is>
       </c>
       <c r="B3713" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Contrib. Soc. - MJM - Renegociação de Obrigações Previdenciárias</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3713" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3714">
       <c r="A3714" t="inlineStr">
         <is>
-          <t>7300000000000</t>
+          <t>7219991205000</t>
         </is>
       </c>
       <c r="B3714" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Receita Patrimonial</t>
+          <t>Rec. Intra. - Demais Contrib. Soc. - MJM - Renegociação de Obrigações Previdenciárias</t>
         </is>
       </c>
       <c r="C3714" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3715">
       <c r="A3715" t="inlineStr">
         <is>
-          <t>7310000000000</t>
+          <t>7300000000000</t>
         </is>
       </c>
       <c r="B3715" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Exploração do Patrimônio Imobiliário do Estado</t>
+          <t>Rec. Intra. - Receita Patrimonial</t>
         </is>
       </c>
       <c r="C3715" t="inlineStr">
@@ -63512,7 +63512,7 @@
     <row r="3716">
       <c r="A3716" t="inlineStr">
         <is>
-          <t>7311000000000</t>
+          <t>7310000000000</t>
         </is>
       </c>
       <c r="B3716" t="inlineStr">
@@ -63529,12 +63529,12 @@
     <row r="3717">
       <c r="A3717" t="inlineStr">
         <is>
-          <t>7311010000000</t>
+          <t>7311000000000</t>
         </is>
       </c>
       <c r="B3717" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aluguéis, Arrendamentos, Foros, Laudêmios, Tarifas de Ocupação</t>
+          <t>Rec. Intra. - Exploração do Patrimônio Imobiliário do Estado</t>
         </is>
       </c>
       <c r="C3717" t="inlineStr">
@@ -63546,12 +63546,12 @@
     <row r="3718">
       <c r="A3718" t="inlineStr">
         <is>
-          <t>7311011000000</t>
+          <t>7311010000000</t>
         </is>
       </c>
       <c r="B3718" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aluguéis e Arrendamentos</t>
+          <t>Rec. Intra. - Aluguéis, Arrendamentos, Foros, Laudêmios, Tarifas de Ocupação</t>
         </is>
       </c>
       <c r="C3718" t="inlineStr">
@@ -63563,12 +63563,12 @@
     <row r="3719">
       <c r="A3719" t="inlineStr">
         <is>
-          <t>7311011100000</t>
+          <t>7311011000000</t>
         </is>
       </c>
       <c r="B3719" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aluguéis Arrendamentos - Principal</t>
+          <t>Rec. Intra. - Aluguéis e Arrendamentos</t>
         </is>
       </c>
       <c r="C3719" t="inlineStr">
@@ -63580,46 +63580,46 @@
     <row r="3720">
       <c r="A3720" t="inlineStr">
         <is>
-          <t>7311011101000</t>
+          <t>7311011100000</t>
         </is>
       </c>
       <c r="B3720" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aluguéis Arrendamentos - Princ. - Aluguéis</t>
+          <t>Rec. Intra. - Aluguéis Arrendamentos - Principal</t>
         </is>
       </c>
       <c r="C3720" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3721">
       <c r="A3721" t="inlineStr">
         <is>
-          <t>7311020000000</t>
+          <t>7311011101000</t>
         </is>
       </c>
       <c r="B3721" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Concessão, Permissão, Autorização ou Cessão do Direito de Uso de Bens Imóveis Públicos</t>
+          <t>Rec. Intra. - Aluguéis Arrendamentos - Princ. - Aluguéis</t>
         </is>
       </c>
       <c r="C3721" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3722">
       <c r="A3722" t="inlineStr">
         <is>
-          <t>7311020100000</t>
+          <t>7311020000000</t>
         </is>
       </c>
       <c r="B3722" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Conc. Perm. Autor. Cessão Dir. Uso Bens Imóv. Púb. - Principal</t>
+          <t>Rec. Intra. - Concessão, Permissão, Autorização ou Cessão do Direito de Uso de Bens Imóveis Públicos</t>
         </is>
       </c>
       <c r="C3722" t="inlineStr">
@@ -63631,46 +63631,46 @@
     <row r="3723">
       <c r="A3723" t="inlineStr">
         <is>
-          <t>7311020101000</t>
+          <t>7311020100000</t>
         </is>
       </c>
       <c r="B3723" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Conc. Perm. Autor. Cessão Dir. Uso Bens Imóv. Púb. - Princ. - Concessão de Direito Real de Uso de Área Pública</t>
+          <t>Rec. Intra. - Conc. Perm. Autor. Cessão Dir. Uso Bens Imóv. Púb. - Principal</t>
         </is>
       </c>
       <c r="C3723" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3724">
       <c r="A3724" t="inlineStr">
         <is>
-          <t>7340000000000</t>
+          <t>7311020101000</t>
         </is>
       </c>
       <c r="B3724" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Exploração de Recursos Naturais</t>
+          <t>Rec. Intra. - Conc. Perm. Autor. Cessão Dir. Uso Bens Imóv. Púb. - Princ. - Concessão de Direito Real de Uso de Área Pública</t>
         </is>
       </c>
       <c r="C3724" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3725">
       <c r="A3725" t="inlineStr">
         <is>
-          <t>7345000000000</t>
+          <t>7340000000000</t>
         </is>
       </c>
       <c r="B3725" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Exploração de Recursos Hídricos</t>
+          <t>Rec. Intra. - Exploração de Recursos Naturais</t>
         </is>
       </c>
       <c r="C3725" t="inlineStr">
@@ -63682,12 +63682,12 @@
     <row r="3726">
       <c r="A3726" t="inlineStr">
         <is>
-          <t>7345010000000</t>
+          <t>7345000000000</t>
         </is>
       </c>
       <c r="B3726" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outorga de Direitos de Uso de Recursos Hídricos</t>
+          <t>Rec. Intra. - Exploração de Recursos Hídricos</t>
         </is>
       </c>
       <c r="C3726" t="inlineStr">
@@ -63699,12 +63699,12 @@
     <row r="3727">
       <c r="A3727" t="inlineStr">
         <is>
-          <t>7345010100000</t>
+          <t>7345010000000</t>
         </is>
       </c>
       <c r="B3727" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outorga Dir. Uso Recursos Hídricos - Principal</t>
+          <t>Rec. Intra. - Outorga de Direitos de Uso de Recursos Hídricos</t>
         </is>
       </c>
       <c r="C3727" t="inlineStr">
@@ -63716,46 +63716,46 @@
     <row r="3728">
       <c r="A3728" t="inlineStr">
         <is>
-          <t>7345010101000</t>
+          <t>7345010100000</t>
         </is>
       </c>
       <c r="B3728" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outorga Dir. Uso Recursos Hídricos - Princ.</t>
+          <t>Rec. Intra. - Outorga Dir. Uso Recursos Hídricos - Principal</t>
         </is>
       </c>
       <c r="C3728" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3729">
       <c r="A3729" t="inlineStr">
         <is>
-          <t>7349000000000</t>
+          <t>7345010101000</t>
         </is>
       </c>
       <c r="B3729" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Exploração de Outros Recursos Naturais</t>
+          <t>Rec. Intra. - Outorga Dir. Uso Recursos Hídricos - Princ.</t>
         </is>
       </c>
       <c r="C3729" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3730">
       <c r="A3730" t="inlineStr">
         <is>
-          <t>7349010000000</t>
+          <t>7349000000000</t>
         </is>
       </c>
       <c r="B3730" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Compensações Ambientais</t>
+          <t>Rec. Intra. - Exploração de Outros Recursos Naturais</t>
         </is>
       </c>
       <c r="C3730" t="inlineStr">
@@ -63767,12 +63767,12 @@
     <row r="3731">
       <c r="A3731" t="inlineStr">
         <is>
-          <t>7349010100000</t>
+          <t>7349010000000</t>
         </is>
       </c>
       <c r="B3731" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Compensações Ambientais - Principal</t>
+          <t>Rec. Intra. - Compensações Ambientais</t>
         </is>
       </c>
       <c r="C3731" t="inlineStr">
@@ -63784,46 +63784,46 @@
     <row r="3732">
       <c r="A3732" t="inlineStr">
         <is>
-          <t>7349010103000</t>
+          <t>7349010100000</t>
         </is>
       </c>
       <c r="B3732" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Compensações Ambientais - Princ. - Supressão do Pequi</t>
+          <t>Rec. Intra. - Compensações Ambientais - Principal</t>
         </is>
       </c>
       <c r="C3732" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3733">
       <c r="A3733" t="inlineStr">
         <is>
-          <t>7390000000000</t>
+          <t>7349010103000</t>
         </is>
       </c>
       <c r="B3733" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Receitas Patrimoniais</t>
+          <t>Rec. Intra. - Compensações Ambientais - Princ. - Supressão do Pequi</t>
         </is>
       </c>
       <c r="C3733" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3734">
       <c r="A3734" t="inlineStr">
         <is>
-          <t>7399000000000</t>
+          <t>7390000000000</t>
         </is>
       </c>
       <c r="B3734" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Receitas Patrimoniais</t>
+          <t>Rec. Intra. - Demais Receitas Patrimoniais</t>
         </is>
       </c>
       <c r="C3734" t="inlineStr">
@@ -63835,7 +63835,7 @@
     <row r="3735">
       <c r="A3735" t="inlineStr">
         <is>
-          <t>7399990000000</t>
+          <t>7399000000000</t>
         </is>
       </c>
       <c r="B3735" t="inlineStr">
@@ -63852,12 +63852,12 @@
     <row r="3736">
       <c r="A3736" t="inlineStr">
         <is>
-          <t>7399990300000</t>
+          <t>7399990000000</t>
         </is>
       </c>
       <c r="B3736" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. Patrimoniais - Dívida Ativa</t>
+          <t>Rec. Intra. - Outras Receitas Patrimoniais</t>
         </is>
       </c>
       <c r="C3736" t="inlineStr">
@@ -63869,75 +63869,75 @@
     <row r="3737">
       <c r="A3737" t="inlineStr">
         <is>
-          <t>7399990301000</t>
+          <t>7399990300000</t>
         </is>
       </c>
       <c r="B3737" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. Patrimoniais - DA</t>
+          <t>Rec. Intra. - Outras Rec. Patrimoniais - Dívida Ativa</t>
         </is>
       </c>
       <c r="C3737" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3738">
       <c r="A3738" t="inlineStr">
         <is>
-          <t>7399990400000</t>
+          <t>7399990301000</t>
         </is>
       </c>
       <c r="B3738" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. Patrimoniais - Dívida Ativa - Multas e Juros de Mora</t>
+          <t>Rec. Intra. - Outras Rec. Patrimoniais - DA</t>
         </is>
       </c>
       <c r="C3738" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3739">
       <c r="A3739" t="inlineStr">
         <is>
-          <t>7399990401000</t>
+          <t>7399990400000</t>
         </is>
       </c>
       <c r="B3739" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. Patrimoniais - DA-MJM</t>
+          <t>Rec. Intra. - Outras Rec. Patrimoniais - Dívida Ativa - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3739" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3740">
       <c r="A3740" t="inlineStr">
         <is>
-          <t>7400000000000</t>
+          <t>7399990401000</t>
         </is>
       </c>
       <c r="B3740" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Receita Agropecuária</t>
+          <t>Rec. Intra. - Outras Rec. Patrimoniais - DA-MJM</t>
         </is>
       </c>
       <c r="C3740" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3741">
       <c r="A3741" t="inlineStr">
         <is>
-          <t>7410000000000</t>
+          <t>7400000000000</t>
         </is>
       </c>
       <c r="B3741" t="inlineStr">
@@ -63954,7 +63954,7 @@
     <row r="3742">
       <c r="A3742" t="inlineStr">
         <is>
-          <t>7411000000000</t>
+          <t>7410000000000</t>
         </is>
       </c>
       <c r="B3742" t="inlineStr">
@@ -63971,7 +63971,7 @@
     <row r="3743">
       <c r="A3743" t="inlineStr">
         <is>
-          <t>7411010000000</t>
+          <t>7411000000000</t>
         </is>
       </c>
       <c r="B3743" t="inlineStr">
@@ -63988,12 +63988,12 @@
     <row r="3744">
       <c r="A3744" t="inlineStr">
         <is>
-          <t>7411010100000</t>
+          <t>7411010000000</t>
         </is>
       </c>
       <c r="B3744" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Agropecuária - Principal</t>
+          <t>Rec. Intra. - Receita Agropecuária</t>
         </is>
       </c>
       <c r="C3744" t="inlineStr">
@@ -64005,109 +64005,109 @@
     <row r="3745">
       <c r="A3745" t="inlineStr">
         <is>
-          <t>7411010101000</t>
+          <t>7411010100000</t>
         </is>
       </c>
       <c r="B3745" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Agropecuária - Princ. - Produção Vegetal</t>
+          <t>Rec. Intra. - Rec. Agropecuária - Principal</t>
         </is>
       </c>
       <c r="C3745" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3746">
       <c r="A3746" t="inlineStr">
         <is>
-          <t>7411010300000</t>
+          <t>7411010101000</t>
         </is>
       </c>
       <c r="B3746" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Agropecuária - Dívida Ativa</t>
+          <t>Rec. Intra. - Rec. Agropecuária - Princ. - Produção Vegetal</t>
         </is>
       </c>
       <c r="C3746" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3747">
       <c r="A3747" t="inlineStr">
         <is>
-          <t>7411010399000</t>
+          <t>7411010300000</t>
         </is>
       </c>
       <c r="B3747" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Agropecuária - DA - Demais</t>
+          <t>Rec. Intra. - Rec. Agropecuária - Dívida Ativa</t>
         </is>
       </c>
       <c r="C3747" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3748">
       <c r="A3748" t="inlineStr">
         <is>
-          <t>7411010400000</t>
+          <t>7411010399000</t>
         </is>
       </c>
       <c r="B3748" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Agropecuária - Dívida Ativa - Multas e Juros de Mora</t>
+          <t>Rec. Intra. - Rec. Agropecuária - DA - Demais</t>
         </is>
       </c>
       <c r="C3748" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3749">
       <c r="A3749" t="inlineStr">
         <is>
-          <t>7411010499000</t>
+          <t>7411010400000</t>
         </is>
       </c>
       <c r="B3749" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Agropecuária - DA-MJM - Demais</t>
+          <t>Rec. Intra. - Rec. Agropecuária - Dívida Ativa - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3749" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3750">
       <c r="A3750" t="inlineStr">
         <is>
-          <t>7500000000000</t>
+          <t>7411010499000</t>
         </is>
       </c>
       <c r="B3750" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Receita Industrial</t>
+          <t>Rec. Intra. - Rec. Agropecuária - DA-MJM - Demais</t>
         </is>
       </c>
       <c r="C3750" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3751">
       <c r="A3751" t="inlineStr">
         <is>
-          <t>7510000000000</t>
+          <t>7500000000000</t>
         </is>
       </c>
       <c r="B3751" t="inlineStr">
@@ -64124,7 +64124,7 @@
     <row r="3752">
       <c r="A3752" t="inlineStr">
         <is>
-          <t>7511000000000</t>
+          <t>7510000000000</t>
         </is>
       </c>
       <c r="B3752" t="inlineStr">
@@ -64141,7 +64141,7 @@
     <row r="3753">
       <c r="A3753" t="inlineStr">
         <is>
-          <t>7511010000000</t>
+          <t>7511000000000</t>
         </is>
       </c>
       <c r="B3753" t="inlineStr">
@@ -64158,12 +64158,12 @@
     <row r="3754">
       <c r="A3754" t="inlineStr">
         <is>
-          <t>7511010100000</t>
+          <t>7511010000000</t>
         </is>
       </c>
       <c r="B3754" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Industrial - Principal</t>
+          <t>Rec. Intra. - Receita Industrial</t>
         </is>
       </c>
       <c r="C3754" t="inlineStr">
@@ -64175,12 +64175,12 @@
     <row r="3755">
       <c r="A3755" t="inlineStr">
         <is>
-          <t>7511010101000</t>
+          <t>7511010100000</t>
         </is>
       </c>
       <c r="B3755" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria de Transformação</t>
+          <t>Rec. Intra. - Rec. Industrial - Principal</t>
         </is>
       </c>
       <c r="C3755" t="inlineStr">
@@ -64192,29 +64192,29 @@
     <row r="3756">
       <c r="A3756" t="inlineStr">
         <is>
-          <t>7511010101003</t>
+          <t>7511010101000</t>
         </is>
       </c>
       <c r="B3756" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria Transformação - Indústria de Produtos Farmacêuticos e Veterinários</t>
+          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria de Transformação</t>
         </is>
       </c>
       <c r="C3756" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3757">
       <c r="A3757" t="inlineStr">
         <is>
-          <t>7511010101004</t>
+          <t>7511010101003</t>
         </is>
       </c>
       <c r="B3757" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria Transformação - Indústria de Produtos Alimentares</t>
+          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria Transformação - Indústria de Produtos Farmacêuticos e Veterinários</t>
         </is>
       </c>
       <c r="C3757" t="inlineStr">
@@ -64226,46 +64226,46 @@
     <row r="3758">
       <c r="A3758" t="inlineStr">
         <is>
-          <t>7511010102000</t>
+          <t>7511010101004</t>
         </is>
       </c>
       <c r="B3758" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria Editorial e Gráfica</t>
+          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria Transformação - Indústria de Produtos Alimentares</t>
         </is>
       </c>
       <c r="C3758" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3759">
       <c r="A3759" t="inlineStr">
         <is>
-          <t>7511010102001</t>
+          <t>7511010102000</t>
         </is>
       </c>
       <c r="B3759" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria Editorial Gráfica - Receita de Publicações</t>
+          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria Editorial e Gráfica</t>
         </is>
       </c>
       <c r="C3759" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3760">
       <c r="A3760" t="inlineStr">
         <is>
-          <t>7511010102002</t>
+          <t>7511010102001</t>
         </is>
       </c>
       <c r="B3760" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria Editorial Gráfica - Assinatura do Jornal Minas Gerais</t>
+          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria Editorial Gráfica - Receita de Publicações</t>
         </is>
       </c>
       <c r="C3760" t="inlineStr">
@@ -64277,12 +64277,12 @@
     <row r="3761">
       <c r="A3761" t="inlineStr">
         <is>
-          <t>7511010102003</t>
+          <t>7511010102002</t>
         </is>
       </c>
       <c r="B3761" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria Editorial Gráfica - Receita de Venda de Assinaturas Via Internet</t>
+          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria Editorial Gráfica - Assinatura do Jornal Minas Gerais</t>
         </is>
       </c>
       <c r="C3761" t="inlineStr">
@@ -64294,97 +64294,97 @@
     <row r="3762">
       <c r="A3762" t="inlineStr">
         <is>
-          <t>7511010300000</t>
+          <t>7511010102003</t>
         </is>
       </c>
       <c r="B3762" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Industrial - Dívida Ativa</t>
+          <t>Rec. Intra. - Rec. Industrial - Princ. - Indústria Editorial Gráfica - Receita de Venda de Assinaturas Via Internet</t>
         </is>
       </c>
       <c r="C3762" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3763">
       <c r="A3763" t="inlineStr">
         <is>
-          <t>7511010399000</t>
+          <t>7511010300000</t>
         </is>
       </c>
       <c r="B3763" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Industrial - DA - Demais</t>
+          <t>Rec. Intra. - Rec. Industrial - Dívida Ativa</t>
         </is>
       </c>
       <c r="C3763" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3764">
       <c r="A3764" t="inlineStr">
         <is>
-          <t>7511010400000</t>
+          <t>7511010399000</t>
         </is>
       </c>
       <c r="B3764" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Industrial - Dívida Ativa - Multas e Juros de Mora</t>
+          <t>Rec. Intra. - Rec. Industrial - DA - Demais</t>
         </is>
       </c>
       <c r="C3764" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3765">
       <c r="A3765" t="inlineStr">
         <is>
-          <t>7511010499000</t>
+          <t>7511010400000</t>
         </is>
       </c>
       <c r="B3765" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Rec. Industrial - DA-MJM - Demais</t>
+          <t>Rec. Intra. - Rec. Industrial - Dívida Ativa - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3765" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3766">
       <c r="A3766" t="inlineStr">
         <is>
-          <t>7600000000000</t>
+          <t>7511010499000</t>
         </is>
       </c>
       <c r="B3766" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Receita de Serviços</t>
+          <t>Rec. Intra. - Rec. Industrial - DA-MJM - Demais</t>
         </is>
       </c>
       <c r="C3766" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3767">
       <c r="A3767" t="inlineStr">
         <is>
-          <t>7610000000000</t>
+          <t>7600000000000</t>
         </is>
       </c>
       <c r="B3767" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Administrativos e Comerciais Gerais</t>
+          <t>Rec. Intra. - Receita de Serviços</t>
         </is>
       </c>
       <c r="C3767" t="inlineStr">
@@ -64396,7 +64396,7 @@
     <row r="3768">
       <c r="A3768" t="inlineStr">
         <is>
-          <t>7611000000000</t>
+          <t>7610000000000</t>
         </is>
       </c>
       <c r="B3768" t="inlineStr">
@@ -64413,7 +64413,7 @@
     <row r="3769">
       <c r="A3769" t="inlineStr">
         <is>
-          <t>7611010000000</t>
+          <t>7611000000000</t>
         </is>
       </c>
       <c r="B3769" t="inlineStr">
@@ -64430,12 +64430,12 @@
     <row r="3770">
       <c r="A3770" t="inlineStr">
         <is>
-          <t>7611010100000</t>
+          <t>7611010000000</t>
         </is>
       </c>
       <c r="B3770" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Principal</t>
+          <t>Rec. Intra. - Serviços Administrativos e Comerciais Gerais</t>
         </is>
       </c>
       <c r="C3770" t="inlineStr">
@@ -64447,29 +64447,29 @@
     <row r="3771">
       <c r="A3771" t="inlineStr">
         <is>
-          <t>7611010101000</t>
+          <t>7611010100000</t>
         </is>
       </c>
       <c r="B3771" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Princ. - Administração de Depósitos Judiciais</t>
+          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Principal</t>
         </is>
       </c>
       <c r="C3771" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3772">
       <c r="A3772" t="inlineStr">
         <is>
-          <t>7611010112000</t>
+          <t>7611010101000</t>
         </is>
       </c>
       <c r="B3772" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Princ. - Fornecimento de Listagens</t>
+          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Princ. - Administração de Depósitos Judiciais</t>
         </is>
       </c>
       <c r="C3772" t="inlineStr">
@@ -64481,12 +64481,12 @@
     <row r="3773">
       <c r="A3773" t="inlineStr">
         <is>
-          <t>7611010114000</t>
+          <t>7611010112000</t>
         </is>
       </c>
       <c r="B3773" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Princ. - Concessão de Outorga</t>
+          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Princ. - Fornecimento de Listagens</t>
         </is>
       </c>
       <c r="C3773" t="inlineStr">
@@ -64498,12 +64498,12 @@
     <row r="3774">
       <c r="A3774" t="inlineStr">
         <is>
-          <t>7611010124000</t>
+          <t>7611010114000</t>
         </is>
       </c>
       <c r="B3774" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Princ. - Educacionais e Capacitação</t>
+          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Princ. - Concessão de Outorga</t>
         </is>
       </c>
       <c r="C3774" t="inlineStr">
@@ -64515,12 +64515,12 @@
     <row r="3775">
       <c r="A3775" t="inlineStr">
         <is>
-          <t>7611010128000</t>
+          <t>7611010124000</t>
         </is>
       </c>
       <c r="B3775" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Princ. - Consultoria, Assistência Técnica e Análise de Projetos</t>
+          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Princ. - Educacionais e Capacitação</t>
         </is>
       </c>
       <c r="C3775" t="inlineStr">
@@ -64532,12 +64532,12 @@
     <row r="3776">
       <c r="A3776" t="inlineStr">
         <is>
-          <t>7611010130000</t>
+          <t>7611010128000</t>
         </is>
       </c>
       <c r="B3776" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Princ. - Estudos e Pesquisa</t>
+          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Princ. - Consultoria, Assistência Técnica e Análise de Projetos</t>
         </is>
       </c>
       <c r="C3776" t="inlineStr">
@@ -64549,29 +64549,29 @@
     <row r="3777">
       <c r="A3777" t="inlineStr">
         <is>
-          <t>7611030000000</t>
+          <t>7611010130000</t>
         </is>
       </c>
       <c r="B3777" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços de Registro, Certificação e Fiscalização</t>
+          <t>Rec. Intra. - Serviços Adm. Comerc. Ger. - Princ. - Estudos e Pesquisa</t>
         </is>
       </c>
       <c r="C3777" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3778">
       <c r="A3778" t="inlineStr">
         <is>
-          <t>7611030100000</t>
+          <t>7611030000000</t>
         </is>
       </c>
       <c r="B3778" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Reg. Certif. Fiscaliz. - Principal</t>
+          <t>Rec. Intra. - Serviços de Registro, Certificação e Fiscalização</t>
         </is>
       </c>
       <c r="C3778" t="inlineStr">
@@ -64583,46 +64583,46 @@
     <row r="3779">
       <c r="A3779" t="inlineStr">
         <is>
-          <t>7611030106000</t>
+          <t>7611030100000</t>
         </is>
       </c>
       <c r="B3779" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Reg. Certif. Fiscaliz. - Princ. - Registro do Comércio</t>
+          <t>Rec. Intra. - Serviços Reg. Certif. Fiscaliz. - Principal</t>
         </is>
       </c>
       <c r="C3779" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3780">
       <c r="A3780" t="inlineStr">
         <is>
-          <t>7611040000000</t>
+          <t>7611030106000</t>
         </is>
       </c>
       <c r="B3780" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços de Informação e Tecnologia</t>
+          <t>Rec. Intra. - Serviços Reg. Certif. Fiscaliz. - Princ. - Registro do Comércio</t>
         </is>
       </c>
       <c r="C3780" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3781">
       <c r="A3781" t="inlineStr">
         <is>
-          <t>7611040100000</t>
+          <t>7611040000000</t>
         </is>
       </c>
       <c r="B3781" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Informação Tecnologia - Principal</t>
+          <t>Rec. Intra. - Serviços de Informação e Tecnologia</t>
         </is>
       </c>
       <c r="C3781" t="inlineStr">
@@ -64634,46 +64634,46 @@
     <row r="3782">
       <c r="A3782" t="inlineStr">
         <is>
-          <t>7611040199000</t>
+          <t>7611040100000</t>
         </is>
       </c>
       <c r="B3782" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Informação Tecnologia - Princ. - Demais Serviços Tecnológicos</t>
+          <t>Rec. Intra. - Serviços Informação Tecnologia - Principal</t>
         </is>
       </c>
       <c r="C3782" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3783">
       <c r="A3783" t="inlineStr">
         <is>
-          <t>7630000000000</t>
+          <t>7611040199000</t>
         </is>
       </c>
       <c r="B3783" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços e Atividades Referentes à Saúde</t>
+          <t>Rec. Intra. - Serviços Informação Tecnologia - Princ. - Demais Serviços Tecnológicos</t>
         </is>
       </c>
       <c r="C3783" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3784">
       <c r="A3784" t="inlineStr">
         <is>
-          <t>7631000000000</t>
+          <t>7630000000000</t>
         </is>
       </c>
       <c r="B3784" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços de Atendimento à Saúde</t>
+          <t>Rec. Intra. - Serviços e Atividades Referentes à Saúde</t>
         </is>
       </c>
       <c r="C3784" t="inlineStr">
@@ -64685,12 +64685,12 @@
     <row r="3785">
       <c r="A3785" t="inlineStr">
         <is>
-          <t>7631500000000</t>
+          <t>7631000000000</t>
         </is>
       </c>
       <c r="B3785" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Hospitalares</t>
+          <t>Rec. Intra. - Serviços de Atendimento à Saúde</t>
         </is>
       </c>
       <c r="C3785" t="inlineStr">
@@ -64702,12 +64702,12 @@
     <row r="3786">
       <c r="A3786" t="inlineStr">
         <is>
-          <t>7631500100000</t>
+          <t>7631500000000</t>
         </is>
       </c>
       <c r="B3786" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Hospitalares - Principal</t>
+          <t>Rec. Intra. - Serviços Hospitalares</t>
         </is>
       </c>
       <c r="C3786" t="inlineStr">
@@ -64719,46 +64719,46 @@
     <row r="3787">
       <c r="A3787" t="inlineStr">
         <is>
-          <t>7631500101000</t>
+          <t>7631500100000</t>
         </is>
       </c>
       <c r="B3787" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Hospitalares - Princ.</t>
+          <t>Rec. Intra. - Serviços Hospitalares - Principal</t>
         </is>
       </c>
       <c r="C3787" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3788">
       <c r="A3788" t="inlineStr">
         <is>
-          <t>7631520000000</t>
+          <t>7631500101000</t>
         </is>
       </c>
       <c r="B3788" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Radiológicos e Laboratoriais</t>
+          <t>Rec. Intra. - Serviços Hospitalares - Princ.</t>
         </is>
       </c>
       <c r="C3788" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3789">
       <c r="A3789" t="inlineStr">
         <is>
-          <t>7631520100000</t>
+          <t>7631520000000</t>
         </is>
       </c>
       <c r="B3789" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Radiológicos Laboratoriais - Principal</t>
+          <t>Rec. Intra. - Serviços Radiológicos e Laboratoriais</t>
         </is>
       </c>
       <c r="C3789" t="inlineStr">
@@ -64770,46 +64770,46 @@
     <row r="3790">
       <c r="A3790" t="inlineStr">
         <is>
-          <t>7631520101000</t>
+          <t>7631520100000</t>
         </is>
       </c>
       <c r="B3790" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Serviços Radiológicos Laboratoriais - Princ.</t>
+          <t>Rec. Intra. - Serviços Radiológicos Laboratoriais - Principal</t>
         </is>
       </c>
       <c r="C3790" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3791">
       <c r="A3791" t="inlineStr">
         <is>
-          <t>7631990000000</t>
+          <t>7631520101000</t>
         </is>
       </c>
       <c r="B3791" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serviços de Atendimento à Saúde</t>
+          <t>Rec. Intra. - Serviços Radiológicos Laboratoriais - Princ.</t>
         </is>
       </c>
       <c r="C3791" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3792">
       <c r="A3792" t="inlineStr">
         <is>
-          <t>7631990100000</t>
+          <t>7631990000000</t>
         </is>
       </c>
       <c r="B3792" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serv. Atend. Saúde - Principal</t>
+          <t>Rec. Intra. - Outros Serviços de Atendimento à Saúde</t>
         </is>
       </c>
       <c r="C3792" t="inlineStr">
@@ -64821,29 +64821,29 @@
     <row r="3793">
       <c r="A3793" t="inlineStr">
         <is>
-          <t>7631990103000</t>
+          <t>7631990100000</t>
         </is>
       </c>
       <c r="B3793" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serv. Atend. Saúde - Princ. - Serviços de Saúde Prestados ao SIA/SUS</t>
+          <t>Rec. Intra. - Outros Serv. Atend. Saúde - Principal</t>
         </is>
       </c>
       <c r="C3793" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3794">
       <c r="A3794" t="inlineStr">
         <is>
-          <t>7631990106000</t>
+          <t>7631990103000</t>
         </is>
       </c>
       <c r="B3794" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serv. Atend. Saúde - Princ. - Serviços de Saúde Prestados - Demais</t>
+          <t>Rec. Intra. - Outros Serv. Atend. Saúde - Princ. - Serviços de Saúde Prestados ao SIA/SUS</t>
         </is>
       </c>
       <c r="C3794" t="inlineStr">
@@ -64855,58 +64855,58 @@
     <row r="3795">
       <c r="A3795" t="inlineStr">
         <is>
-          <t>7631990200000</t>
+          <t>7631990106000</t>
         </is>
       </c>
       <c r="B3795" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serv. Atend. Saúde - Multas e Juros de Mora</t>
+          <t>Rec. Intra. - Outros Serv. Atend. Saúde - Princ. - Serviços de Saúde Prestados - Demais</t>
         </is>
       </c>
       <c r="C3795" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3796">
       <c r="A3796" t="inlineStr">
         <is>
-          <t>7631990206000</t>
+          <t>7631990200000</t>
         </is>
       </c>
       <c r="B3796" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serv. Atend. Saúde - MJM - Serviços de Saúde Prestados - Demais</t>
+          <t>Rec. Intra. - Outros Serv. Atend. Saúde - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3796" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3797">
       <c r="A3797" t="inlineStr">
         <is>
-          <t>7690000000000</t>
+          <t>7631990206000</t>
         </is>
       </c>
       <c r="B3797" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serviços</t>
+          <t>Rec. Intra. - Outros Serv. Atend. Saúde - MJM - Serviços de Saúde Prestados - Demais</t>
         </is>
       </c>
       <c r="C3797" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3798">
       <c r="A3798" t="inlineStr">
         <is>
-          <t>7699000000000</t>
+          <t>7690000000000</t>
         </is>
       </c>
       <c r="B3798" t="inlineStr">
@@ -64923,7 +64923,7 @@
     <row r="3799">
       <c r="A3799" t="inlineStr">
         <is>
-          <t>7699990000000</t>
+          <t>7699000000000</t>
         </is>
       </c>
       <c r="B3799" t="inlineStr">
@@ -64940,12 +64940,12 @@
     <row r="3800">
       <c r="A3800" t="inlineStr">
         <is>
-          <t>7699990100000</t>
+          <t>7699990000000</t>
         </is>
       </c>
       <c r="B3800" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serviços - Principal</t>
+          <t>Rec. Intra. - Outros Serviços</t>
         </is>
       </c>
       <c r="C3800" t="inlineStr">
@@ -64957,114 +64957,114 @@
     <row r="3801">
       <c r="A3801" t="inlineStr">
         <is>
-          <t>7699990101000</t>
+          <t>7699990100000</t>
         </is>
       </c>
       <c r="B3801" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serviços - Princ.</t>
+          <t>Rec. Intra. - Outros Serviços - Principal</t>
         </is>
       </c>
       <c r="C3801" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3802">
       <c r="A3802" t="inlineStr">
         <is>
-          <t>7699990300000</t>
+          <t>7699990101000</t>
         </is>
       </c>
       <c r="B3802" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serviços - Dívida Ativa</t>
+          <t>Rec. Intra. - Outros Serviços - Princ.</t>
         </is>
       </c>
       <c r="C3802" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3803">
       <c r="A3803" t="inlineStr">
         <is>
-          <t>7699990301000</t>
+          <t>7699990300000</t>
         </is>
       </c>
       <c r="B3803" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serviços - DA</t>
+          <t>Rec. Intra. - Outros Serviços - Dívida Ativa</t>
         </is>
       </c>
       <c r="C3803" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3804">
       <c r="A3804" t="inlineStr">
         <is>
-          <t>7699990400000</t>
+          <t>7699990301000</t>
         </is>
       </c>
       <c r="B3804" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serviços - Dívida Ativa - Multas e Juros de Mora</t>
+          <t>Rec. Intra. - Outros Serviços - DA</t>
         </is>
       </c>
       <c r="C3804" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3805">
       <c r="A3805" t="inlineStr">
         <is>
-          <t>7699990401000</t>
+          <t>7699990400000</t>
         </is>
       </c>
       <c r="B3805" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Serviços - DA-MJM</t>
+          <t>Rec. Intra. - Outros Serviços - Dívida Ativa - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3805" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3806">
       <c r="A3806" t="inlineStr">
         <is>
-          <t>7700000000000</t>
+          <t>7699990401000</t>
         </is>
       </c>
       <c r="B3806" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Transferências Correntes</t>
+          <t>Rec. Intra. - Outros Serviços - DA-MJM</t>
         </is>
       </c>
       <c r="C3806" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3807">
       <c r="A3807" t="inlineStr">
         <is>
-          <t>7720000000000</t>
+          <t>7700000000000</t>
         </is>
       </c>
       <c r="B3807" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Transferências dos Estados e do Distrito Federal e de suas Entidades</t>
+          <t>Rec. Intra. - Transferências Correntes</t>
         </is>
       </c>
       <c r="C3807" t="inlineStr">
@@ -65076,12 +65076,12 @@
     <row r="3808">
       <c r="A3808" t="inlineStr">
         <is>
-          <t>7721000000000</t>
+          <t>7720000000000</t>
         </is>
       </c>
       <c r="B3808" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Participação na Receita dos Estados e Distrito Federal</t>
+          <t>Rec. Intra. - Transferências dos Estados e do Distrito Federal e de suas Entidades</t>
         </is>
       </c>
       <c r="C3808" t="inlineStr">
@@ -65093,12 +65093,12 @@
     <row r="3809">
       <c r="A3809" t="inlineStr">
         <is>
-          <t>7723000000000</t>
+          <t>7721000000000</t>
         </is>
       </c>
       <c r="B3809" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Transferências de Recursos do Sistema Único de Saúde - SUS</t>
+          <t>Rec. Intra. - Participação na Receita dos Estados e Distrito Federal</t>
         </is>
       </c>
       <c r="C3809" t="inlineStr">
@@ -65110,12 +65110,12 @@
     <row r="3810">
       <c r="A3810" t="inlineStr">
         <is>
-          <t>7729000000000</t>
+          <t>7723000000000</t>
         </is>
       </c>
       <c r="B3810" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Transferências dos Estados e Distrito Federal</t>
+          <t>Rec. Intra. - Transferências de Recursos do Sistema Único de Saúde - SUS</t>
         </is>
       </c>
       <c r="C3810" t="inlineStr">
@@ -65127,12 +65127,12 @@
     <row r="3811">
       <c r="A3811" t="inlineStr">
         <is>
-          <t>7729520000000</t>
+          <t>7729000000000</t>
         </is>
       </c>
       <c r="B3811" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Transferências de Recursos Destinados a Programas de Educação</t>
+          <t>Rec. Intra. - Outras Transferências dos Estados e Distrito Federal</t>
         </is>
       </c>
       <c r="C3811" t="inlineStr">
@@ -65144,12 +65144,12 @@
     <row r="3812">
       <c r="A3812" t="inlineStr">
         <is>
-          <t>7729990000000</t>
+          <t>7729520000000</t>
         </is>
       </c>
       <c r="B3812" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Transferências dos Estados e DF</t>
+          <t>Rec. Intra. - Transferências de Recursos Destinados a Programas de Educação</t>
         </is>
       </c>
       <c r="C3812" t="inlineStr">
@@ -65161,12 +65161,12 @@
     <row r="3813">
       <c r="A3813" t="inlineStr">
         <is>
-          <t>7729990100000</t>
+          <t>7729990000000</t>
         </is>
       </c>
       <c r="B3813" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Transf. Estados DF - Principal</t>
+          <t>Rec. Intra. - Outras Transferências dos Estados e DF</t>
         </is>
       </c>
       <c r="C3813" t="inlineStr">
@@ -65178,29 +65178,29 @@
     <row r="3814">
       <c r="A3814" t="inlineStr">
         <is>
-          <t>7729990125000</t>
+          <t>7729990100000</t>
         </is>
       </c>
       <c r="B3814" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Transf. Estados DF - Princ. - Repasse do Fundo Estadual de Saúde - FES - LC Federal nº 141/12</t>
+          <t>Rec. Intra. - Outras Transf. Estados DF - Principal</t>
         </is>
       </c>
       <c r="C3814" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3815">
       <c r="A3815" t="inlineStr">
         <is>
-          <t>7729990126000</t>
+          <t>7729990125000</t>
         </is>
       </c>
       <c r="B3815" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Transf. Estados DF - Princ. - Repasse do Fundo Estadual de Proteção e Defesa do Consumidor - FEPDC</t>
+          <t>Rec. Intra. - Outras Transf. Estados DF - Princ. - Repasse do Fundo Estadual de Saúde - FES - LC Federal nº 141/12</t>
         </is>
       </c>
       <c r="C3815" t="inlineStr">
@@ -65212,12 +65212,12 @@
     <row r="3816">
       <c r="A3816" t="inlineStr">
         <is>
-          <t>7729990127000</t>
+          <t>7729990126000</t>
         </is>
       </c>
       <c r="B3816" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Transf. Estados DF - Princ. - Repasse do Fundo Especial do Ministério Público do Estado de Minas Gerais - FUNEMP</t>
+          <t>Rec. Intra. - Outras Transf. Estados DF - Princ. - Repasse do Fundo Estadual de Proteção e Defesa do Consumidor - FEPDC</t>
         </is>
       </c>
       <c r="C3816" t="inlineStr">
@@ -65229,29 +65229,29 @@
     <row r="3817">
       <c r="A3817" t="inlineStr">
         <is>
-          <t>7900000000000</t>
+          <t>7729990127000</t>
         </is>
       </c>
       <c r="B3817" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Receitas Correntes</t>
+          <t>Rec. Intra. - Outras Transf. Estados DF - Princ. - Repasse do Fundo Especial do Ministério Público do Estado de Minas Gerais - FUNEMP</t>
         </is>
       </c>
       <c r="C3817" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3818">
       <c r="A3818" t="inlineStr">
         <is>
-          <t>7920000000000</t>
+          <t>7900000000000</t>
         </is>
       </c>
       <c r="B3818" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Indenizações, Restituições e Ressarcimentos</t>
+          <t>Rec. Intra. - Outras Receitas Correntes</t>
         </is>
       </c>
       <c r="C3818" t="inlineStr">
@@ -65263,12 +65263,12 @@
     <row r="3819">
       <c r="A3819" t="inlineStr">
         <is>
-          <t>7921000000000</t>
+          <t>7920000000000</t>
         </is>
       </c>
       <c r="B3819" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Indenizações</t>
+          <t>Rec. Intra. - Indenizações, Restituições e Ressarcimentos</t>
         </is>
       </c>
       <c r="C3819" t="inlineStr">
@@ -65280,12 +65280,12 @@
     <row r="3820">
       <c r="A3820" t="inlineStr">
         <is>
-          <t>7921990000000</t>
+          <t>7921000000000</t>
         </is>
       </c>
       <c r="B3820" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Indenizações</t>
+          <t>Rec. Intra. - Indenizações</t>
         </is>
       </c>
       <c r="C3820" t="inlineStr">
@@ -65297,12 +65297,12 @@
     <row r="3821">
       <c r="A3821" t="inlineStr">
         <is>
-          <t>7921990100000</t>
+          <t>7921990000000</t>
         </is>
       </c>
       <c r="B3821" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Indenizações - Principal</t>
+          <t>Rec. Intra. - Outras Indenizações</t>
         </is>
       </c>
       <c r="C3821" t="inlineStr">
@@ -65314,46 +65314,46 @@
     <row r="3822">
       <c r="A3822" t="inlineStr">
         <is>
-          <t>7921990199000</t>
+          <t>7921990100000</t>
         </is>
       </c>
       <c r="B3822" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Indenizações - Princ. - Demais</t>
+          <t>Rec. Intra. - Outras Indenizações - Principal</t>
         </is>
       </c>
       <c r="C3822" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3823">
       <c r="A3823" t="inlineStr">
         <is>
-          <t>7922000000000</t>
+          <t>7921990199000</t>
         </is>
       </c>
       <c r="B3823" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Restituições</t>
+          <t>Rec. Intra. - Outras Indenizações - Princ. - Demais</t>
         </is>
       </c>
       <c r="C3823" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3824">
       <c r="A3824" t="inlineStr">
         <is>
-          <t>7922990000000</t>
+          <t>7922000000000</t>
         </is>
       </c>
       <c r="B3824" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Restituições</t>
+          <t>Rec. Intra. - Restituições</t>
         </is>
       </c>
       <c r="C3824" t="inlineStr">
@@ -65365,12 +65365,12 @@
     <row r="3825">
       <c r="A3825" t="inlineStr">
         <is>
-          <t>7922990100000</t>
+          <t>7922990000000</t>
         </is>
       </c>
       <c r="B3825" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Restituições - Principal</t>
+          <t>Rec. Intra. - Outras Restituições</t>
         </is>
       </c>
       <c r="C3825" t="inlineStr">
@@ -65382,46 +65382,46 @@
     <row r="3826">
       <c r="A3826" t="inlineStr">
         <is>
-          <t>7922990199000</t>
+          <t>7922990100000</t>
         </is>
       </c>
       <c r="B3826" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Restituições - Princ. - Demais</t>
+          <t>Rec. Intra. - Outras Restituições - Principal</t>
         </is>
       </c>
       <c r="C3826" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3827">
       <c r="A3827" t="inlineStr">
         <is>
-          <t>7923000000000</t>
+          <t>7922990199000</t>
         </is>
       </c>
       <c r="B3827" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Ressarcimentos</t>
+          <t>Rec. Intra. - Outras Restituições - Princ. - Demais</t>
         </is>
       </c>
       <c r="C3827" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3828">
       <c r="A3828" t="inlineStr">
         <is>
-          <t>7923990000000</t>
+          <t>7923000000000</t>
         </is>
       </c>
       <c r="B3828" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Ressarcimentos</t>
+          <t>Rec. Intra. - Ressarcimentos</t>
         </is>
       </c>
       <c r="C3828" t="inlineStr">
@@ -65433,12 +65433,12 @@
     <row r="3829">
       <c r="A3829" t="inlineStr">
         <is>
-          <t>7923990100000</t>
+          <t>7923990000000</t>
         </is>
       </c>
       <c r="B3829" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Ressarcimentos - Principal</t>
+          <t>Rec. Intra. - Outros Ressarcimentos</t>
         </is>
       </c>
       <c r="C3829" t="inlineStr">
@@ -65450,29 +65450,29 @@
     <row r="3830">
       <c r="A3830" t="inlineStr">
         <is>
-          <t>7923990101000</t>
+          <t>7923990100000</t>
         </is>
       </c>
       <c r="B3830" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Ressarcimentos - Princ. - Retenção sobre Pagamento Folha de Sentenciado</t>
+          <t>Rec. Intra. - Outros Ressarcimentos - Principal</t>
         </is>
       </c>
       <c r="C3830" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3831">
       <c r="A3831" t="inlineStr">
         <is>
-          <t>7923990102000</t>
+          <t>7923990101000</t>
         </is>
       </c>
       <c r="B3831" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outros Ressarcimentos - Princ. - Pagamento Direto Sentenciado</t>
+          <t>Rec. Intra. - Outros Ressarcimentos - Princ. - Retenção sobre Pagamento Folha de Sentenciado</t>
         </is>
       </c>
       <c r="C3831" t="inlineStr">
@@ -65484,29 +65484,29 @@
     <row r="3832">
       <c r="A3832" t="inlineStr">
         <is>
-          <t>7990000000000</t>
+          <t>7923990102000</t>
         </is>
       </c>
       <c r="B3832" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Demais Receitas Correntes</t>
+          <t>Rec. Intra. - Outros Ressarcimentos - Princ. - Pagamento Direto Sentenciado</t>
         </is>
       </c>
       <c r="C3832" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3833">
       <c r="A3833" t="inlineStr">
         <is>
-          <t>7999000000000</t>
+          <t>7990000000000</t>
         </is>
       </c>
       <c r="B3833" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Receitas Correntes</t>
+          <t>Rec. Intra. - Demais Receitas Correntes</t>
         </is>
       </c>
       <c r="C3833" t="inlineStr">
@@ -65518,12 +65518,12 @@
     <row r="3834">
       <c r="A3834" t="inlineStr">
         <is>
-          <t>7999010000000</t>
+          <t>7999000000000</t>
         </is>
       </c>
       <c r="B3834" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aportes Periódicos para Amortização de Déficit Atuarial do Regimes Próprios de Previdência e Sistema de Proteção Social</t>
+          <t>Rec. Intra. - Outras Receitas Correntes</t>
         </is>
       </c>
       <c r="C3834" t="inlineStr">
@@ -65535,12 +65535,12 @@
     <row r="3835">
       <c r="A3835" t="inlineStr">
         <is>
-          <t>7999010100000</t>
+          <t>7999010000000</t>
         </is>
       </c>
       <c r="B3835" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Principal</t>
+          <t>Rec. Intra. - Aportes Periódicos para Amortização de Déficit Atuarial do Regimes Próprios de Previdência e Sistema de Proteção Social</t>
         </is>
       </c>
       <c r="C3835" t="inlineStr">
@@ -65552,29 +65552,29 @@
     <row r="3836">
       <c r="A3836" t="inlineStr">
         <is>
-          <t>7999010101000</t>
+          <t>7999010100000</t>
         </is>
       </c>
       <c r="B3836" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Poder Executivo</t>
+          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Principal</t>
         </is>
       </c>
       <c r="C3836" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3837">
       <c r="A3837" t="inlineStr">
         <is>
-          <t>7999010102000</t>
+          <t>7999010101000</t>
         </is>
       </c>
       <c r="B3837" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Assembleia Legislativa do Estado de Minas Gerais - ALMG</t>
+          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Poder Executivo</t>
         </is>
       </c>
       <c r="C3837" t="inlineStr">
@@ -65586,12 +65586,12 @@
     <row r="3838">
       <c r="A3838" t="inlineStr">
         <is>
-          <t>7999010103000</t>
+          <t>7999010102000</t>
         </is>
       </c>
       <c r="B3838" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Tribunal de Contas do Estado de Minas Gerais - TCEMG</t>
+          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Assembleia Legislativa do Estado de Minas Gerais - ALMG</t>
         </is>
       </c>
       <c r="C3838" t="inlineStr">
@@ -65603,12 +65603,12 @@
     <row r="3839">
       <c r="A3839" t="inlineStr">
         <is>
-          <t>7999010104000</t>
+          <t>7999010103000</t>
         </is>
       </c>
       <c r="B3839" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Tribunal de Justiça do Estado de Minas Gerais - TJMG</t>
+          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Tribunal de Contas do Estado de Minas Gerais - TCEMG</t>
         </is>
       </c>
       <c r="C3839" t="inlineStr">
@@ -65620,12 +65620,12 @@
     <row r="3840">
       <c r="A3840" t="inlineStr">
         <is>
-          <t>7999010105000</t>
+          <t>7999010104000</t>
         </is>
       </c>
       <c r="B3840" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Tribunal de Justiça Militar do Estado de Minas Gerais - TJMMG</t>
+          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Tribunal de Justiça do Estado de Minas Gerais - TJMG</t>
         </is>
       </c>
       <c r="C3840" t="inlineStr">
@@ -65637,12 +65637,12 @@
     <row r="3841">
       <c r="A3841" t="inlineStr">
         <is>
-          <t>7999010106000</t>
+          <t>7999010105000</t>
         </is>
       </c>
       <c r="B3841" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Ministério Público do Estado de Minas Gerais - MPMG</t>
+          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Tribunal de Justiça Militar do Estado de Minas Gerais - TJMMG</t>
         </is>
       </c>
       <c r="C3841" t="inlineStr">
@@ -65654,12 +65654,12 @@
     <row r="3842">
       <c r="A3842" t="inlineStr">
         <is>
-          <t>7999010107000</t>
+          <t>7999010106000</t>
         </is>
       </c>
       <c r="B3842" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Defensoria Pública do Estado de Minas Gerais - DEFPUB</t>
+          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Ministério Público do Estado de Minas Gerais - MPMG</t>
         </is>
       </c>
       <c r="C3842" t="inlineStr">
@@ -65671,29 +65671,29 @@
     <row r="3843">
       <c r="A3843" t="inlineStr">
         <is>
-          <t>7999990000000</t>
+          <t>7999010107000</t>
         </is>
       </c>
       <c r="B3843" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Receitas</t>
+          <t>Rec. Intra. - Aportes Amortiz. Déficit RPPS Sist. Proteção Social - Princ. - Defensoria Pública do Estado de Minas Gerais - DEFPUB</t>
         </is>
       </c>
       <c r="C3843" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3844">
       <c r="A3844" t="inlineStr">
         <is>
-          <t>7999992000000</t>
+          <t>7999990000000</t>
         </is>
       </c>
       <c r="B3844" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Receitas Não Arrecadadas e Não Projetadas pela RFB - Primárias</t>
+          <t>Rec. Intra. - Outras Receitas</t>
         </is>
       </c>
       <c r="C3844" t="inlineStr">
@@ -65705,12 +65705,12 @@
     <row r="3845">
       <c r="A3845" t="inlineStr">
         <is>
-          <t>7999992100000</t>
+          <t>7999992000000</t>
         </is>
       </c>
       <c r="B3845" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Principal</t>
+          <t>Rec. Intra. - Outras Receitas Não Arrecadadas e Não Projetadas pela RFB - Primárias</t>
         </is>
       </c>
       <c r="C3845" t="inlineStr">
@@ -65722,29 +65722,29 @@
     <row r="3846">
       <c r="A3846" t="inlineStr">
         <is>
-          <t>7999992105000</t>
+          <t>7999992100000</t>
         </is>
       </c>
       <c r="B3846" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Reserva Técnica Obrigatória - Equilíbrio Atuarial</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Principal</t>
         </is>
       </c>
       <c r="C3846" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3847">
       <c r="A3847" t="inlineStr">
         <is>
-          <t>7999992106000</t>
+          <t>7999992105000</t>
         </is>
       </c>
       <c r="B3847" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Assistência Complementar - Assembleia Legislativa do Estado de Minas Gerais - ALMG</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Reserva Técnica Obrigatória - Equilíbrio Atuarial</t>
         </is>
       </c>
       <c r="C3847" t="inlineStr">
@@ -65756,46 +65756,46 @@
     <row r="3848">
       <c r="A3848" t="inlineStr">
         <is>
-          <t>7999992114000</t>
+          <t>7999992106000</t>
         </is>
       </c>
       <c r="B3848" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte para Cobertura de Insuficiência Financeira do Regime Próprio de Previdência Social - RPPS</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Assistência Complementar - Assembleia Legislativa do Estado de Minas Gerais - ALMG</t>
         </is>
       </c>
       <c r="C3848" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3849">
       <c r="A3849" t="inlineStr">
         <is>
-          <t>7999992114001</t>
+          <t>7999992114000</t>
         </is>
       </c>
       <c r="B3849" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Poder Executivo</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte para Cobertura de Insuficiência Financeira do Regime Próprio de Previdência Social - RPPS</t>
         </is>
       </c>
       <c r="C3849" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3850">
       <c r="A3850" t="inlineStr">
         <is>
-          <t>7999992114002</t>
+          <t>7999992114001</t>
         </is>
       </c>
       <c r="B3850" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Assembleia Legislativa do Estado de Minas Gerais</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Poder Executivo</t>
         </is>
       </c>
       <c r="C3850" t="inlineStr">
@@ -65807,12 +65807,12 @@
     <row r="3851">
       <c r="A3851" t="inlineStr">
         <is>
-          <t>7999992114003</t>
+          <t>7999992114002</t>
         </is>
       </c>
       <c r="B3851" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Tribunal de Contas do Estado de Minas Gerais</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Assembleia Legislativa do Estado de Minas Gerais</t>
         </is>
       </c>
       <c r="C3851" t="inlineStr">
@@ -65824,12 +65824,12 @@
     <row r="3852">
       <c r="A3852" t="inlineStr">
         <is>
-          <t>7999992114004</t>
+          <t>7999992114003</t>
         </is>
       </c>
       <c r="B3852" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Tribunal de Justiça do Estado de Minas Gerais</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Tribunal de Contas do Estado de Minas Gerais</t>
         </is>
       </c>
       <c r="C3852" t="inlineStr">
@@ -65841,12 +65841,12 @@
     <row r="3853">
       <c r="A3853" t="inlineStr">
         <is>
-          <t>7999992114005</t>
+          <t>7999992114004</t>
         </is>
       </c>
       <c r="B3853" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Tribunal de Justiça Militar do Estado de Minas Gerais</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Tribunal de Justiça do Estado de Minas Gerais</t>
         </is>
       </c>
       <c r="C3853" t="inlineStr">
@@ -65858,12 +65858,12 @@
     <row r="3854">
       <c r="A3854" t="inlineStr">
         <is>
-          <t>7999992114006</t>
+          <t>7999992114005</t>
         </is>
       </c>
       <c r="B3854" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Ministério Público do Estado de Minas Gerais</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Tribunal de Justiça Militar do Estado de Minas Gerais</t>
         </is>
       </c>
       <c r="C3854" t="inlineStr">
@@ -65875,12 +65875,12 @@
     <row r="3855">
       <c r="A3855" t="inlineStr">
         <is>
-          <t>7999992114007</t>
+          <t>7999992114006</t>
         </is>
       </c>
       <c r="B3855" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Defensoria Pública do Estado de Minas Gerais</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Ministério Público do Estado de Minas Gerais</t>
         </is>
       </c>
       <c r="C3855" t="inlineStr">
@@ -65892,12 +65892,12 @@
     <row r="3856">
       <c r="A3856" t="inlineStr">
         <is>
-          <t>7999992118000</t>
+          <t>7999992114007</t>
         </is>
       </c>
       <c r="B3856" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Recomposição da Compensação Financeira dos Regimes de Previdência</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Aporte Insuficiência Financeira RPPS - Defensoria Pública do Estado de Minas Gerais</t>
         </is>
       </c>
       <c r="C3856" t="inlineStr">
@@ -65909,12 +65909,12 @@
     <row r="3857">
       <c r="A3857" t="inlineStr">
         <is>
-          <t>7999992199000</t>
+          <t>7999992118000</t>
         </is>
       </c>
       <c r="B3857" t="inlineStr">
         <is>
-          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Demais</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Recomposição da Compensação Financeira dos Regimes de Previdência</t>
         </is>
       </c>
       <c r="C3857" t="inlineStr">
@@ -65926,29 +65926,29 @@
     <row r="3858">
       <c r="A3858" t="inlineStr">
         <is>
-          <t>9000000000000</t>
+          <t>7999992199000</t>
         </is>
       </c>
       <c r="B3858" t="inlineStr">
         <is>
-          <t>Dedução das Receitas</t>
+          <t>Rec. Intra. - Outras Rec. - Primárias - Princ. - Demais</t>
         </is>
       </c>
       <c r="C3858" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3859">
       <c r="A3859" t="inlineStr">
         <is>
-          <t>9100000000000</t>
+          <t>9000000000000</t>
         </is>
       </c>
       <c r="B3859" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Impostos, Taxas e Contribuições de Melhoria</t>
+          <t>Dedução das Receitas</t>
         </is>
       </c>
       <c r="C3859" t="inlineStr">
@@ -65960,12 +65960,12 @@
     <row r="3860">
       <c r="A3860" t="inlineStr">
         <is>
-          <t>9110000000000</t>
+          <t>9100000000000</t>
         </is>
       </c>
       <c r="B3860" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Impostos</t>
+          <t>Dedução Rec. - Impostos, Taxas e Contribuições de Melhoria</t>
         </is>
       </c>
       <c r="C3860" t="inlineStr">
@@ -65977,12 +65977,12 @@
     <row r="3861">
       <c r="A3861" t="inlineStr">
         <is>
-          <t>9112000000000</t>
+          <t>9110000000000</t>
         </is>
       </c>
       <c r="B3861" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Imposto sobre o Patrimônio</t>
+          <t>Dedução Rec. - Impostos</t>
         </is>
       </c>
       <c r="C3861" t="inlineStr">
@@ -65994,12 +65994,12 @@
     <row r="3862">
       <c r="A3862" t="inlineStr">
         <is>
-          <t>9112510000000</t>
+          <t>9112000000000</t>
         </is>
       </c>
       <c r="B3862" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Imposto sobre a Propriedade de Veículos Automotores</t>
+          <t>Dedução Rec. - Imposto sobre o Patrimônio</t>
         </is>
       </c>
       <c r="C3862" t="inlineStr">
@@ -66011,12 +66011,12 @@
     <row r="3863">
       <c r="A3863" t="inlineStr">
         <is>
-          <t>9112510100000</t>
+          <t>9112510000000</t>
         </is>
       </c>
       <c r="B3863" t="inlineStr">
         <is>
-          <t>Dedução Rec. - IPVA - Principal</t>
+          <t>Dedução Rec. - Imposto sobre a Propriedade de Veículos Automotores</t>
         </is>
       </c>
       <c r="C3863" t="inlineStr">
@@ -66028,29 +66028,29 @@
     <row r="3864">
       <c r="A3864" t="inlineStr">
         <is>
-          <t>9112510102000</t>
+          <t>9112510100000</t>
         </is>
       </c>
       <c r="B3864" t="inlineStr">
         <is>
-          <t>Dedução Rec. - IPVA - Princ. - Cota Parte dos Municípios</t>
+          <t>Dedução Rec. - IPVA - Principal</t>
         </is>
       </c>
       <c r="C3864" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3865">
       <c r="A3865" t="inlineStr">
         <is>
-          <t>9112510103000</t>
+          <t>9112510102000</t>
         </is>
       </c>
       <c r="B3865" t="inlineStr">
         <is>
-          <t>Dedução Rec. - IPVA - Princ. - Cota Parte do Estado para o FUNDEB</t>
+          <t>Dedução Rec. - IPVA - Princ. - Cota Parte dos Municípios</t>
         </is>
       </c>
       <c r="C3865" t="inlineStr">
@@ -66062,46 +66062,46 @@
     <row r="3866">
       <c r="A3866" t="inlineStr">
         <is>
-          <t>9112510200000</t>
+          <t>9112510103000</t>
         </is>
       </c>
       <c r="B3866" t="inlineStr">
         <is>
-          <t>Dedução Rec. - IPVA - Multas e Juros de Mora</t>
+          <t>Dedução Rec. - IPVA - Princ. - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3866" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3867">
       <c r="A3867" t="inlineStr">
         <is>
-          <t>9112510202000</t>
+          <t>9112510200000</t>
         </is>
       </c>
       <c r="B3867" t="inlineStr">
         <is>
-          <t>Dedução Rec. - IPVA - MJM - Cota Parte dos Municípios</t>
+          <t>Dedução Rec. - IPVA - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3867" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3868">
       <c r="A3868" t="inlineStr">
         <is>
-          <t>9112510203000</t>
+          <t>9112510202000</t>
         </is>
       </c>
       <c r="B3868" t="inlineStr">
         <is>
-          <t>Dedução Rec. - IPVA - MJM - Cota Parte do Estado para o FUNDEB</t>
+          <t>Dedução Rec. - IPVA - MJM - Cota Parte dos Municípios</t>
         </is>
       </c>
       <c r="C3868" t="inlineStr">
@@ -66113,46 +66113,46 @@
     <row r="3869">
       <c r="A3869" t="inlineStr">
         <is>
-          <t>9112510300000</t>
+          <t>9112510203000</t>
         </is>
       </c>
       <c r="B3869" t="inlineStr">
         <is>
-          <t>Dedução Rec. - IPVA - Dívida Ativa</t>
+          <t>Dedução Rec. - IPVA - MJM - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3869" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3870">
       <c r="A3870" t="inlineStr">
         <is>
-          <t>9112510302000</t>
+          <t>9112510300000</t>
         </is>
       </c>
       <c r="B3870" t="inlineStr">
         <is>
-          <t>Dedução Rec. - IPVA - DA - Cota Parte dos Municípios</t>
+          <t>Dedução Rec. - IPVA - Dívida Ativa</t>
         </is>
       </c>
       <c r="C3870" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3871">
       <c r="A3871" t="inlineStr">
         <is>
-          <t>9112510303000</t>
+          <t>9112510302000</t>
         </is>
       </c>
       <c r="B3871" t="inlineStr">
         <is>
-          <t>Dedução Rec. - IPVA - DA - Cota Parte do Estado para o FUNDEB</t>
+          <t>Dedução Rec. - IPVA - DA - Cota Parte dos Municípios</t>
         </is>
       </c>
       <c r="C3871" t="inlineStr">
@@ -66164,46 +66164,46 @@
     <row r="3872">
       <c r="A3872" t="inlineStr">
         <is>
-          <t>9112510400000</t>
+          <t>9112510303000</t>
         </is>
       </c>
       <c r="B3872" t="inlineStr">
         <is>
-          <t>Dedução Rec. - IPVA - Dívida Ativa - Multas e Juros de Mora</t>
+          <t>Dedução Rec. - IPVA - DA - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3872" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3873">
       <c r="A3873" t="inlineStr">
         <is>
-          <t>9112510402000</t>
+          <t>9112510400000</t>
         </is>
       </c>
       <c r="B3873" t="inlineStr">
         <is>
-          <t>Dedução Rec. - IPVA - DA - Cota Parte dos Municipios</t>
+          <t>Dedução Rec. - IPVA - Dívida Ativa - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3873" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3874">
       <c r="A3874" t="inlineStr">
         <is>
-          <t>9112510403000</t>
+          <t>9112510402000</t>
         </is>
       </c>
       <c r="B3874" t="inlineStr">
         <is>
-          <t>Dedução Rec. - IPVA - DA - Cota Parte do Estado para o FUNDEB</t>
+          <t>Dedução Rec. - IPVA - DA - Cota Parte dos Municipios</t>
         </is>
       </c>
       <c r="C3874" t="inlineStr">
@@ -66215,29 +66215,29 @@
     <row r="3875">
       <c r="A3875" t="inlineStr">
         <is>
-          <t>9112520000000</t>
+          <t>9112510403000</t>
         </is>
       </c>
       <c r="B3875" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Imposto sobre Transmissão “Causa Mortis” e Doação de Bens e Direitos</t>
+          <t>Dedução Rec. - IPVA - DA - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3875" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3876">
       <c r="A3876" t="inlineStr">
         <is>
-          <t>9112520100000</t>
+          <t>9112520000000</t>
         </is>
       </c>
       <c r="B3876" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ITCD - Principal</t>
+          <t>Dedução Rec. - Imposto sobre Transmissão “Causa Mortis” e Doação de Bens e Direitos</t>
         </is>
       </c>
       <c r="C3876" t="inlineStr">
@@ -66249,143 +66249,143 @@
     <row r="3877">
       <c r="A3877" t="inlineStr">
         <is>
-          <t>9112520102000</t>
+          <t>9112520100000</t>
         </is>
       </c>
       <c r="B3877" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ITCD - Princ. - Cota Parte do Estado para o FUNDEB</t>
+          <t>Dedução Rec. - ITCD - Principal</t>
         </is>
       </c>
       <c r="C3877" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3878">
       <c r="A3878" t="inlineStr">
         <is>
-          <t>9112520200000</t>
+          <t>9112520102000</t>
         </is>
       </c>
       <c r="B3878" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ITCD - Multas e Juros de Mora</t>
+          <t>Dedução Rec. - ITCD - Princ. - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3878" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3879">
       <c r="A3879" t="inlineStr">
         <is>
-          <t>9112520202000</t>
+          <t>9112520200000</t>
         </is>
       </c>
       <c r="B3879" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ITCD - MJM - Cota Parte do Estado para o FUNDEB</t>
+          <t>Dedução Rec. - ITCD - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3879" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3880">
       <c r="A3880" t="inlineStr">
         <is>
-          <t>9112520300000</t>
+          <t>9112520202000</t>
         </is>
       </c>
       <c r="B3880" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ITCD - Dívida Ativa</t>
+          <t>Dedução Rec. - ITCD - MJM - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3880" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3881">
       <c r="A3881" t="inlineStr">
         <is>
-          <t>9112520302000</t>
+          <t>9112520300000</t>
         </is>
       </c>
       <c r="B3881" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ITCD - DA - Cota Parte do Estado para o FUNDEB</t>
+          <t>Dedução Rec. - ITCD - Dívida Ativa</t>
         </is>
       </c>
       <c r="C3881" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3882">
       <c r="A3882" t="inlineStr">
         <is>
-          <t>9112520400000</t>
+          <t>9112520302000</t>
         </is>
       </c>
       <c r="B3882" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ITCD - Dívida Ativa - Multas e Juros de Mora</t>
+          <t>Dedução Rec. - ITCD - DA - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3882" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3883">
       <c r="A3883" t="inlineStr">
         <is>
-          <t>9112520402000</t>
+          <t>9112520400000</t>
         </is>
       </c>
       <c r="B3883" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ITCD - DA-MJM - Cota Parte do Estado para o FUNDEB</t>
+          <t>Dedução Rec. - ITCD - Dívida Ativa - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3883" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3884">
       <c r="A3884" t="inlineStr">
         <is>
-          <t>9114000000000</t>
+          <t>9112520402000</t>
         </is>
       </c>
       <c r="B3884" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Impostos sobre a Produção e Circulação de Mercadorias e Serviços</t>
+          <t>Dedução Rec. - ITCD - DA-MJM - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3884" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3885">
       <c r="A3885" t="inlineStr">
         <is>
-          <t>9114500000000</t>
+          <t>9114000000000</t>
         </is>
       </c>
       <c r="B3885" t="inlineStr">
@@ -66402,12 +66402,12 @@
     <row r="3886">
       <c r="A3886" t="inlineStr">
         <is>
-          <t>9114501000000</t>
+          <t>9114500000000</t>
         </is>
       </c>
       <c r="B3886" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Imposto sobre Operações Relativas à Circulação de Mercadorias e sobre Prestações de Serviços de Transporte Interestadual e Intermunicipal e de Comunicação</t>
+          <t>Dedução Rec. - Impostos sobre a Produção e Circulação de Mercadorias e Serviços</t>
         </is>
       </c>
       <c r="C3886" t="inlineStr">
@@ -66419,12 +66419,12 @@
     <row r="3887">
       <c r="A3887" t="inlineStr">
         <is>
-          <t>9114501100000</t>
+          <t>9114501000000</t>
         </is>
       </c>
       <c r="B3887" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - Principal</t>
+          <t>Dedução Rec. - Imposto sobre Operações Relativas à Circulação de Mercadorias e sobre Prestações de Serviços de Transporte Interestadual e Intermunicipal e de Comunicação</t>
         </is>
       </c>
       <c r="C3887" t="inlineStr">
@@ -66436,12 +66436,12 @@
     <row r="3888">
       <c r="A3888" t="inlineStr">
         <is>
-          <t>9114501101000</t>
+          <t>9114501100000</t>
         </is>
       </c>
       <c r="B3888" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - Princ. - Cota Parte do Estado</t>
+          <t>Dedução Rec. - ICMS - Principal</t>
         </is>
       </c>
       <c r="C3888" t="inlineStr">
@@ -66453,29 +66453,29 @@
     <row r="3889">
       <c r="A3889" t="inlineStr">
         <is>
-          <t>9114501101002</t>
+          <t>9114501101000</t>
         </is>
       </c>
       <c r="B3889" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - Princ. - Cota Parte do Estado - Cessão de Direitos Creditórios - Lei Estadual nº 19.266/10</t>
+          <t>Dedução Rec. - ICMS - Princ. - Cota Parte do Estado</t>
         </is>
       </c>
       <c r="C3889" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3890">
       <c r="A3890" t="inlineStr">
         <is>
-          <t>9114501102000</t>
+          <t>9114501101002</t>
         </is>
       </c>
       <c r="B3890" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - Princ. - Cota Parte dos Municípios</t>
+          <t>Dedução Rec. - ICMS - Princ. - Cota Parte do Estado - Cessão de Direitos Creditórios - Lei Estadual nº 19.266/10</t>
         </is>
       </c>
       <c r="C3890" t="inlineStr">
@@ -66487,12 +66487,12 @@
     <row r="3891">
       <c r="A3891" t="inlineStr">
         <is>
-          <t>9114501103000</t>
+          <t>9114501102000</t>
         </is>
       </c>
       <c r="B3891" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - Princ. - Cota Parte do Estado para o FUNDEB</t>
+          <t>Dedução Rec. - ICMS - Princ. - Cota Parte dos Municípios</t>
         </is>
       </c>
       <c r="C3891" t="inlineStr">
@@ -66504,29 +66504,29 @@
     <row r="3892">
       <c r="A3892" t="inlineStr">
         <is>
-          <t>9114501200000</t>
+          <t>9114501103000</t>
         </is>
       </c>
       <c r="B3892" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - Multas e Juros de Mora</t>
+          <t>Dedução Rec. - ICMS - Princ. - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3892" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3893">
       <c r="A3893" t="inlineStr">
         <is>
-          <t>9114501201000</t>
+          <t>9114501200000</t>
         </is>
       </c>
       <c r="B3893" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - MJM - Cota Parte do Estado</t>
+          <t>Dedução Rec. - ICMS - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3893" t="inlineStr">
@@ -66538,29 +66538,29 @@
     <row r="3894">
       <c r="A3894" t="inlineStr">
         <is>
-          <t>9114501201002</t>
+          <t>9114501201000</t>
         </is>
       </c>
       <c r="B3894" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - MJM - Cota Parte do Estado - Cessão de Direitos Creditórios - Lei Estadual nº 19.266/10</t>
+          <t>Dedução Rec. - ICMS - MJM - Cota Parte do Estado</t>
         </is>
       </c>
       <c r="C3894" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3895">
       <c r="A3895" t="inlineStr">
         <is>
-          <t>9114501202000</t>
+          <t>9114501201002</t>
         </is>
       </c>
       <c r="B3895" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - MJM - Cota Parte dos Municípios</t>
+          <t>Dedução Rec. - ICMS - MJM - Cota Parte do Estado - Cessão de Direitos Creditórios - Lei Estadual nº 19.266/10</t>
         </is>
       </c>
       <c r="C3895" t="inlineStr">
@@ -66572,12 +66572,12 @@
     <row r="3896">
       <c r="A3896" t="inlineStr">
         <is>
-          <t>9114501203000</t>
+          <t>9114501202000</t>
         </is>
       </c>
       <c r="B3896" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - MJM - Cota Parte do Estado para o FUNDEB</t>
+          <t>Dedução Rec. - ICMS - MJM - Cota Parte dos Municípios</t>
         </is>
       </c>
       <c r="C3896" t="inlineStr">
@@ -66589,29 +66589,29 @@
     <row r="3897">
       <c r="A3897" t="inlineStr">
         <is>
-          <t>9114501300000</t>
+          <t>9114501203000</t>
         </is>
       </c>
       <c r="B3897" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - Dívida Ativa</t>
+          <t>Dedução Rec. - ICMS - MJM - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3897" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3898">
       <c r="A3898" t="inlineStr">
         <is>
-          <t>9114501301000</t>
+          <t>9114501300000</t>
         </is>
       </c>
       <c r="B3898" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - DA - Cota Parte do Estado</t>
+          <t>Dedução Rec. - ICMS - Dívida Ativa</t>
         </is>
       </c>
       <c r="C3898" t="inlineStr">
@@ -66623,29 +66623,29 @@
     <row r="3899">
       <c r="A3899" t="inlineStr">
         <is>
-          <t>9114501301002</t>
+          <t>9114501301000</t>
         </is>
       </c>
       <c r="B3899" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - DA - Cota Parte do Estado - Cessão de Direitos Creditórios - Lei Estadual nº 19.266/10</t>
+          <t>Dedução Rec. - ICMS - DA - Cota Parte do Estado</t>
         </is>
       </c>
       <c r="C3899" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3900">
       <c r="A3900" t="inlineStr">
         <is>
-          <t>9114501302000</t>
+          <t>9114501301002</t>
         </is>
       </c>
       <c r="B3900" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - DA - Cota Parte dos Municípios</t>
+          <t>Dedução Rec. - ICMS - DA - Cota Parte do Estado - Cessão de Direitos Creditórios - Lei Estadual nº 19.266/10</t>
         </is>
       </c>
       <c r="C3900" t="inlineStr">
@@ -66657,12 +66657,12 @@
     <row r="3901">
       <c r="A3901" t="inlineStr">
         <is>
-          <t>9114501303000</t>
+          <t>9114501302000</t>
         </is>
       </c>
       <c r="B3901" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - DA - Cota Parte do Estado para o FUNDEB</t>
+          <t>Dedução Rec. - ICMS - DA - Cota Parte dos Municípios</t>
         </is>
       </c>
       <c r="C3901" t="inlineStr">
@@ -66674,63 +66674,63 @@
     <row r="3902">
       <c r="A3902" t="inlineStr">
         <is>
-          <t>9114501400000</t>
+          <t>9114501303000</t>
         </is>
       </c>
       <c r="B3902" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - Dívida Ativa - Multas e Juros de Mora</t>
+          <t>Dedução Rec. - ICMS - DA - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3902" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3903">
       <c r="A3903" t="inlineStr">
         <is>
-          <t>9114501403000</t>
+          <t>9114501400000</t>
         </is>
       </c>
       <c r="B3903" t="inlineStr">
         <is>
-          <t>Dedução Rec. - ICMS - DA-MJM - Cota Parte do Estado para o FUNDEB</t>
+          <t>Dedução Rec. - ICMS - Dívida Ativa - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3903" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3904">
       <c r="A3904" t="inlineStr">
         <is>
-          <t>9114502000000</t>
+          <t>9114501403000</t>
         </is>
       </c>
       <c r="B3904" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Adicional ICMS - Fundo Estadual de Combate à Pobreza</t>
+          <t>Dedução Rec. - ICMS - DA-MJM - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3904" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3905">
       <c r="A3905" t="inlineStr">
         <is>
-          <t>9114502100000</t>
+          <t>9114502000000</t>
         </is>
       </c>
       <c r="B3905" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Adicional ICMS - Fundo Estadual Combate Pobreza - Fundo de Erradicação da Miséria - FEM - Principal</t>
+          <t>Dedução Rec. - Adicional ICMS - Fundo Estadual de Combate à Pobreza</t>
         </is>
       </c>
       <c r="C3905" t="inlineStr">
@@ -66742,148 +66742,148 @@
     <row r="3906">
       <c r="A3906" t="inlineStr">
         <is>
-          <t>9114502102000</t>
+          <t>9114502100000</t>
         </is>
       </c>
       <c r="B3906" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Adicional ICMS - FEM - Princ. - Cota Parte do FUNDEB</t>
+          <t>Dedução Rec. - Adicional ICMS - Fundo Estadual Combate Pobreza - Fundo de Erradicação da Miséria - FEM - Principal</t>
         </is>
       </c>
       <c r="C3906" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3907">
       <c r="A3907" t="inlineStr">
         <is>
-          <t>9114502200000</t>
+          <t>9114502102000</t>
         </is>
       </c>
       <c r="B3907" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Adicional ICMS - Fundo Estadual Combate Pobreza - Fundo de Erradicação da Miséria - FEM - Multas e Juros de Mora</t>
+          <t>Dedução Rec. - Adicional ICMS - FEM - Princ. - Cota Parte do FUNDEB</t>
         </is>
       </c>
       <c r="C3907" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3908">
       <c r="A3908" t="inlineStr">
         <is>
-          <t>9114502202000</t>
+          <t>9114502200000</t>
         </is>
       </c>
       <c r="B3908" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Adicional ICMS - FEM - MJM - Cota Parte do FUNDEB</t>
+          <t>Dedução Rec. - Adicional ICMS - Fundo Estadual Combate Pobreza - Fundo de Erradicação da Miséria - FEM - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3908" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3909">
       <c r="A3909" t="inlineStr">
         <is>
-          <t>9114502300000</t>
+          <t>9114502202000</t>
         </is>
       </c>
       <c r="B3909" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Adicional ICMS - Fundo Estadual Combate Pobreza - Fundo de Erradicação da Miséria - FEM - Dívida Ativa</t>
+          <t>Dedução Rec. - Adicional ICMS - FEM - MJM - Cota Parte do FUNDEB</t>
         </is>
       </c>
       <c r="C3909" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3910">
       <c r="A3910" t="inlineStr">
         <is>
-          <t>9114502302000</t>
+          <t>9114502300000</t>
         </is>
       </c>
       <c r="B3910" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Adicional ICMS - FEM - DA - Cota Parte do FUNDEB</t>
+          <t>Dedução Rec. - Adicional ICMS - Fundo Estadual Combate Pobreza - Fundo de Erradicação da Miséria - FEM - Dívida Ativa</t>
         </is>
       </c>
       <c r="C3910" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3911">
       <c r="A3911" t="inlineStr">
         <is>
-          <t>9114502400000</t>
+          <t>9114502302000</t>
         </is>
       </c>
       <c r="B3911" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Adicional ICMS - Fundo Estadual Combate Pobreza - Fundo de Erradicação da Miséria - FEM - Dívida Ativa - Multas e Juros de Mora</t>
+          <t>Dedução Rec. - Adicional ICMS - FEM - DA - Cota Parte do FUNDEB</t>
         </is>
       </c>
       <c r="C3911" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3912">
       <c r="A3912" t="inlineStr">
         <is>
-          <t>9114502402000</t>
+          <t>9114502400000</t>
         </is>
       </c>
       <c r="B3912" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Adicional ICMS - FEM - DA-MJM - Cota Parte do FUNDEB</t>
+          <t>Dedução Rec. - Adicional ICMS - Fundo Estadual Combate Pobreza - Fundo de Erradicação da Miséria - FEM - Dívida Ativa - Multas e Juros de Mora</t>
         </is>
       </c>
       <c r="C3912" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3913">
       <c r="A3913" t="inlineStr">
         <is>
-          <t>9116000000000</t>
+          <t>9114502402000</t>
         </is>
       </c>
       <c r="B3913" t="inlineStr">
         <is>
-          <t>Imposto sobre Bens e/ou Serviços instituídos após a EC nº 132/2023</t>
+          <t>Dedução Rec. - Adicional ICMS - FEM - DA-MJM - Cota Parte do FUNDEB</t>
         </is>
       </c>
       <c r="C3913" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3914">
       <c r="A3914" t="inlineStr">
         <is>
-          <t>9116500000000</t>
+          <t>9116000000000</t>
         </is>
       </c>
       <c r="B3914" t="inlineStr">
         <is>
-          <t>IBS Estado</t>
+          <t>Imposto sobre Bens e/ou Serviços instituídos após a EC nº 132/2023</t>
         </is>
       </c>
       <c r="C3914" t="inlineStr">
@@ -66895,12 +66895,12 @@
     <row r="3915">
       <c r="A3915" t="inlineStr">
         <is>
-          <t>9116500100000</t>
+          <t>9116500000000</t>
         </is>
       </c>
       <c r="B3915" t="inlineStr">
         <is>
-          <t>IBS Estado - Principal</t>
+          <t>IBS Estado</t>
         </is>
       </c>
       <c r="C3915" t="inlineStr">
@@ -66912,29 +66912,29 @@
     <row r="3916">
       <c r="A3916" t="inlineStr">
         <is>
-          <t>9116500101000</t>
+          <t>9116500100000</t>
         </is>
       </c>
       <c r="B3916" t="inlineStr">
         <is>
-          <t>IBS Estado - Princ. - Cota Parte Estado</t>
+          <t>IBS Estado - Principal</t>
         </is>
       </c>
       <c r="C3916" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3917">
       <c r="A3917" t="inlineStr">
         <is>
-          <t>9116500102000</t>
+          <t>9116500101000</t>
         </is>
       </c>
       <c r="B3917" t="inlineStr">
         <is>
-          <t>IBS Estado - Princ. - Cota Parte dos Municípios</t>
+          <t>IBS Estado - Princ. - Cota Parte Estado</t>
         </is>
       </c>
       <c r="C3917" t="inlineStr">
@@ -66946,12 +66946,12 @@
     <row r="3918">
       <c r="A3918" t="inlineStr">
         <is>
-          <t>9116500103000</t>
+          <t>9116500102000</t>
         </is>
       </c>
       <c r="B3918" t="inlineStr">
         <is>
-          <t>IBS Estado - Princ. - Cota Parte do Estado para o FUNDEB</t>
+          <t>IBS Estado - Princ. - Cota Parte dos Municípios</t>
         </is>
       </c>
       <c r="C3918" t="inlineStr">
@@ -66963,12 +66963,12 @@
     <row r="3919">
       <c r="A3919" t="inlineStr">
         <is>
-          <t>9116500104000</t>
+          <t>9116500103000</t>
         </is>
       </c>
       <c r="B3919" t="inlineStr">
         <is>
-          <t>IBS Estado - Princ. - Cota Parte do Estado para o Comitê Gestor do IBS</t>
+          <t>IBS Estado - Princ. - Cota Parte do Estado para o FUNDEB</t>
         </is>
       </c>
       <c r="C3919" t="inlineStr">
@@ -66980,29 +66980,29 @@
     <row r="3920">
       <c r="A3920" t="inlineStr">
         <is>
-          <t>9300000000000</t>
+          <t>9116500104000</t>
         </is>
       </c>
       <c r="B3920" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Receita Patrimonial</t>
+          <t>IBS Estado - Princ. - Cota Parte do Estado para o Comitê Gestor do IBS</t>
         </is>
       </c>
       <c r="C3920" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3921">
       <c r="A3921" t="inlineStr">
         <is>
-          <t>9320000000000</t>
+          <t>9300000000000</t>
         </is>
       </c>
       <c r="B3921" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Valores Mobiliários</t>
+          <t>Dedução Rec. - Receita Patrimonial</t>
         </is>
       </c>
       <c r="C3921" t="inlineStr">
@@ -67014,12 +67014,12 @@
     <row r="3922">
       <c r="A3922" t="inlineStr">
         <is>
-          <t>9321000000000</t>
+          <t>9320000000000</t>
         </is>
       </c>
       <c r="B3922" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Juros e Correções Monetárias</t>
+          <t>Dedução Rec. - Valores Mobiliários</t>
         </is>
       </c>
       <c r="C3922" t="inlineStr">
@@ -67031,12 +67031,12 @@
     <row r="3923">
       <c r="A3923" t="inlineStr">
         <is>
-          <t>9321010000000</t>
+          <t>9321000000000</t>
         </is>
       </c>
       <c r="B3923" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Remuneração de Depósitos Bancários</t>
+          <t>Dedução Rec. - Juros e Correções Monetárias</t>
         </is>
       </c>
       <c r="C3923" t="inlineStr">
@@ -67048,12 +67048,12 @@
     <row r="3924">
       <c r="A3924" t="inlineStr">
         <is>
-          <t>9321010100000</t>
+          <t>9321010000000</t>
         </is>
       </c>
       <c r="B3924" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Remuneração Depósitos Bancários - Principal</t>
+          <t>Dedução Rec. - Remuneração de Depósitos Bancários</t>
         </is>
       </c>
       <c r="C3924" t="inlineStr">
@@ -67065,46 +67065,46 @@
     <row r="3925">
       <c r="A3925" t="inlineStr">
         <is>
-          <t>9321010101000</t>
+          <t>9321010100000</t>
         </is>
       </c>
       <c r="B3925" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Remuneração Depósitos Bancários - Princ.</t>
+          <t>Dedução Rec. - Remuneração Depósitos Bancários - Principal</t>
         </is>
       </c>
       <c r="C3925" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3926">
       <c r="A3926" t="inlineStr">
         <is>
-          <t>9321040000000</t>
+          <t>9321010101000</t>
         </is>
       </c>
       <c r="B3926" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Remuneração dos Recursos do Regime Próprio de Previdência Social - RPPS</t>
+          <t>Dedução Rec. - Remuneração Depósitos Bancários - Princ.</t>
         </is>
       </c>
       <c r="C3926" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3927">
       <c r="A3927" t="inlineStr">
         <is>
-          <t>9321040100000</t>
+          <t>9321040000000</t>
         </is>
       </c>
       <c r="B3927" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Remuneração Recursos RPPS - Principal</t>
+          <t>Dedução Rec. - Remuneração dos Recursos do Regime Próprio de Previdência Social - RPPS</t>
         </is>
       </c>
       <c r="C3927" t="inlineStr">
@@ -67116,29 +67116,29 @@
     <row r="3928">
       <c r="A3928" t="inlineStr">
         <is>
-          <t>9321040101000</t>
+          <t>9321040100000</t>
         </is>
       </c>
       <c r="B3928" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Remuneração Recursos RPPS - Princ. - Renda Fixa</t>
+          <t>Dedução Rec. - Remuneração Recursos RPPS - Principal</t>
         </is>
       </c>
       <c r="C3928" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3929">
       <c r="A3929" t="inlineStr">
         <is>
-          <t>9321040102000</t>
+          <t>9321040101000</t>
         </is>
       </c>
       <c r="B3929" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Remuneração Recursos RPPS - Princ. - Renda Variável</t>
+          <t>Dedução Rec. - Remuneração Recursos RPPS - Princ. - Renda Fixa</t>
         </is>
       </c>
       <c r="C3929" t="inlineStr">
@@ -67150,24 +67150,24 @@
     <row r="3930">
       <c r="A3930" t="inlineStr">
         <is>
-          <t>9329000000000</t>
+          <t>9321040102000</t>
         </is>
       </c>
       <c r="B3930" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Outros Valores Mobiliários</t>
+          <t>Dedução Rec. - Remuneração Recursos RPPS - Princ. - Renda Variável</t>
         </is>
       </c>
       <c r="C3930" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3931">
       <c r="A3931" t="inlineStr">
         <is>
-          <t>9329990000000</t>
+          <t>9329000000000</t>
         </is>
       </c>
       <c r="B3931" t="inlineStr">
@@ -67184,12 +67184,12 @@
     <row r="3932">
       <c r="A3932" t="inlineStr">
         <is>
-          <t>9329990100000</t>
+          <t>9329990000000</t>
         </is>
       </c>
       <c r="B3932" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Outros Valores Mobiliários - Principal</t>
+          <t>Dedução Rec. - Outros Valores Mobiliários</t>
         </is>
       </c>
       <c r="C3932" t="inlineStr">
@@ -67201,12 +67201,12 @@
     <row r="3933">
       <c r="A3933" t="inlineStr">
         <is>
-          <t>9329990101000</t>
+          <t>9329990100000</t>
         </is>
       </c>
       <c r="B3933" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Outros Valores Mobiliários - Princ. - Títulos de Responsabilidade do Governo Federal</t>
+          <t>Dedução Rec. - Outros Valores Mobiliários - Principal</t>
         </is>
       </c>
       <c r="C3933" t="inlineStr">
@@ -67218,46 +67218,46 @@
     <row r="3934">
       <c r="A3934" t="inlineStr">
         <is>
-          <t>9329990101001</t>
+          <t>9329990101000</t>
         </is>
       </c>
       <c r="B3934" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Outros Valores Mobiliários - Princ. - Títulos Respons. Gov. Fed. - Vinculado ao Regime Próprio de Previdência Social - RPPS</t>
+          <t>Dedução Rec. - Outros Valores Mobiliários - Princ. - Títulos de Responsabilidade do Governo Federal</t>
         </is>
       </c>
       <c r="C3934" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3935">
       <c r="A3935" t="inlineStr">
         <is>
-          <t>9700000000000</t>
+          <t>9329990101001</t>
         </is>
       </c>
       <c r="B3935" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Transferências Correntes</t>
+          <t>Dedução Rec. - Outros Valores Mobiliários - Princ. - Títulos Respons. Gov. Fed. - Vinculado ao Regime Próprio de Previdência Social - RPPS</t>
         </is>
       </c>
       <c r="C3935" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3936">
       <c r="A3936" t="inlineStr">
         <is>
-          <t>9710000000000</t>
+          <t>9700000000000</t>
         </is>
       </c>
       <c r="B3936" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Transferências da União e de suas Entidades</t>
+          <t>Dedução Rec. - Transferências Correntes</t>
         </is>
       </c>
       <c r="C3936" t="inlineStr">
@@ -67269,12 +67269,12 @@
     <row r="3937">
       <c r="A3937" t="inlineStr">
         <is>
-          <t>9711000000000</t>
+          <t>9710000000000</t>
         </is>
       </c>
       <c r="B3937" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Transferências Decorrentes de Participação na Receita da União</t>
+          <t>Dedução Rec. - Transferências da União e de suas Entidades</t>
         </is>
       </c>
       <c r="C3937" t="inlineStr">
@@ -67286,12 +67286,12 @@
     <row r="3938">
       <c r="A3938" t="inlineStr">
         <is>
-          <t>9711500000000</t>
+          <t>9711000000000</t>
         </is>
       </c>
       <c r="B3938" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Cota-Parte do Fundo de Participação dos Estados e do Distrito Federal - FPE</t>
+          <t>Dedução Rec. - Transferências Decorrentes de Participação na Receita da União</t>
         </is>
       </c>
       <c r="C3938" t="inlineStr">
@@ -67303,12 +67303,12 @@
     <row r="3939">
       <c r="A3939" t="inlineStr">
         <is>
-          <t>9711500100000</t>
+          <t>9711500000000</t>
         </is>
       </c>
       <c r="B3939" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Cota-Parte FPE - Principal</t>
+          <t>Dedução Rec. - Cota-Parte do Fundo de Participação dos Estados e do Distrito Federal - FPE</t>
         </is>
       </c>
       <c r="C3939" t="inlineStr">
@@ -67320,46 +67320,46 @@
     <row r="3940">
       <c r="A3940" t="inlineStr">
         <is>
-          <t>9711500102000</t>
+          <t>9711500100000</t>
         </is>
       </c>
       <c r="B3940" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Cota-Parte FPE - Princ. - FUNDEB</t>
+          <t>Dedução Rec. - Cota-Parte FPE - Principal</t>
         </is>
       </c>
       <c r="C3940" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3941">
       <c r="A3941" t="inlineStr">
         <is>
-          <t>9711530000000</t>
+          <t>9711500102000</t>
         </is>
       </c>
       <c r="B3941" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Cota-Parte do Imposto sobre Produtos Industrializados - Estados Exportadores de Produtos Industrializados</t>
+          <t>Dedução Rec. - Cota-Parte FPE - Princ. - FUNDEB</t>
         </is>
       </c>
       <c r="C3941" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3942">
       <c r="A3942" t="inlineStr">
         <is>
-          <t>9711530100000</t>
+          <t>9711530000000</t>
         </is>
       </c>
       <c r="B3942" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Cota-Parte IPI - Estados Export. Prod. Indust. - Princ.</t>
+          <t>Dedução Rec. - Cota-Parte do Imposto sobre Produtos Industrializados - Estados Exportadores de Produtos Industrializados</t>
         </is>
       </c>
       <c r="C3942" t="inlineStr">
@@ -67371,29 +67371,29 @@
     <row r="3943">
       <c r="A3943" t="inlineStr">
         <is>
-          <t>9711530102000</t>
+          <t>9711530100000</t>
         </is>
       </c>
       <c r="B3943" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Cota-Parte IPI - Estados Export. Prod. Indust. - Princ. - Municípios</t>
+          <t>Dedução Rec. - Cota-Parte IPI - Estados Export. Prod. Indust. - Princ.</t>
         </is>
       </c>
       <c r="C3943" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3944">
       <c r="A3944" t="inlineStr">
         <is>
-          <t>9711530103000</t>
+          <t>9711530102000</t>
         </is>
       </c>
       <c r="B3944" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Cota-Parte IPI - Estados Export. Prod. Indust. - Princ. - FUNDEB</t>
+          <t>Dedução Rec. - Cota-Parte IPI - Estados Export. Prod. Indust. - Princ. - Municípios</t>
         </is>
       </c>
       <c r="C3944" t="inlineStr">
@@ -67405,29 +67405,29 @@
     <row r="3945">
       <c r="A3945" t="inlineStr">
         <is>
-          <t>9711540000000</t>
+          <t>9711530103000</t>
         </is>
       </c>
       <c r="B3945" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Cota-Parte da Contribuição de Intervenção no Domínio Econômico</t>
+          <t>Dedução Rec. - Cota-Parte IPI - Estados Export. Prod. Indust. - Princ. - FUNDEB</t>
         </is>
       </c>
       <c r="C3945" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3946">
       <c r="A3946" t="inlineStr">
         <is>
-          <t>9711540100000</t>
+          <t>9711540000000</t>
         </is>
       </c>
       <c r="B3946" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Cota-Parte CIDE - Principal</t>
+          <t>Dedução Rec. - Cota-Parte da Contribuição de Intervenção no Domínio Econômico</t>
         </is>
       </c>
       <c r="C3946" t="inlineStr">
@@ -67439,46 +67439,46 @@
     <row r="3947">
       <c r="A3947" t="inlineStr">
         <is>
-          <t>9711540102000</t>
+          <t>9711540100000</t>
         </is>
       </c>
       <c r="B3947" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Cota-Parte CIDE - Princ. - Municípios</t>
+          <t>Dedução Rec. - Cota-Parte CIDE - Principal</t>
         </is>
       </c>
       <c r="C3947" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3948">
       <c r="A3948" t="inlineStr">
         <is>
-          <t>9719000000000</t>
+          <t>9711540102000</t>
         </is>
       </c>
       <c r="B3948" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Outras Transferências de Recursos da União e de suas Entidades</t>
+          <t>Dedução Rec. - Cota-Parte CIDE - Princ. - Municípios</t>
         </is>
       </c>
       <c r="C3948" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3949">
       <c r="A3949" t="inlineStr">
         <is>
-          <t>9719510000000</t>
+          <t>9719000000000</t>
         </is>
       </c>
       <c r="B3949" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Transferências Financeiras do ICMS - Desoneração - L.C. Nº 87/96</t>
+          <t>Dedução Rec. - Outras Transferências de Recursos da União e de suas Entidades</t>
         </is>
       </c>
       <c r="C3949" t="inlineStr">
@@ -67490,12 +67490,12 @@
     <row r="3950">
       <c r="A3950" t="inlineStr">
         <is>
-          <t>9719510100000</t>
+          <t>9719510000000</t>
         </is>
       </c>
       <c r="B3950" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Transf. Financeiras ICMS - Desoneração - L.C. nº 87/96 - Principal</t>
+          <t>Dedução Rec. - Transferências Financeiras do ICMS - Desoneração - L.C. Nº 87/96</t>
         </is>
       </c>
       <c r="C3950" t="inlineStr">
@@ -67507,46 +67507,46 @@
     <row r="3951">
       <c r="A3951" t="inlineStr">
         <is>
-          <t>9719510102000</t>
+          <t>9719510100000</t>
         </is>
       </c>
       <c r="B3951" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Transf. Financeiras ICMS - Desoneração - L.C. nº 87/96 - Princ. - FUNDEB</t>
+          <t>Dedução Rec. - Transf. Financeiras ICMS - Desoneração - L.C. nº 87/96 - Principal</t>
         </is>
       </c>
       <c r="C3951" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3952">
       <c r="A3952" t="inlineStr">
         <is>
-          <t>9719610000000</t>
+          <t>9719510102000</t>
         </is>
       </c>
       <c r="B3952" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Auxílio Financeiro – Outorga Crédito Tributário ICMS – Art. 5º, Inciso V, EC nº 123/2022</t>
+          <t>Dedução Rec. - Transf. Financeiras ICMS - Desoneração - L.C. nº 87/96 - Princ. - FUNDEB</t>
         </is>
       </c>
       <c r="C3952" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3953">
       <c r="A3953" t="inlineStr">
         <is>
-          <t>9719610100000</t>
+          <t>9719610000000</t>
         </is>
       </c>
       <c r="B3953" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Auxílio Financ. - Outorga Créd. Tribut. ICMS - EC nº 123/2022 - Principal</t>
+          <t>Dedução Rec. - Auxílio Financeiro – Outorga Crédito Tributário ICMS – Art. 5º, Inciso V, EC nº 123/2022</t>
         </is>
       </c>
       <c r="C3953" t="inlineStr">
@@ -67558,12 +67558,12 @@
     <row r="3954">
       <c r="A3954" t="inlineStr">
         <is>
-          <t>9719610101000</t>
+          <t>9719610100000</t>
         </is>
       </c>
       <c r="B3954" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Auxílio Financ. - Outorga Créd. Tribut. ICMS - EC nº 123/2022 - Princ. - Etanol</t>
+          <t>Dedução Rec. - Auxílio Financ. - Outorga Créd. Tribut. ICMS - EC nº 123/2022 - Principal</t>
         </is>
       </c>
       <c r="C3954" t="inlineStr">
@@ -67575,29 +67575,29 @@
     <row r="3955">
       <c r="A3955" t="inlineStr">
         <is>
-          <t>9719610101002</t>
+          <t>9719610101000</t>
         </is>
       </c>
       <c r="B3955" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Auxílio Financ. - Outorga Créd. Tribut. ICMS - EC nº 123/2022 - Princ. - Etanol - Cota Parte dos Municípios</t>
+          <t>Dedução Rec. - Auxílio Financ. - Outorga Créd. Tribut. ICMS - EC nº 123/2022 - Princ. - Etanol</t>
         </is>
       </c>
       <c r="C3955" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3956">
       <c r="A3956" t="inlineStr">
         <is>
-          <t>9719610101003</t>
+          <t>9719610101002</t>
         </is>
       </c>
       <c r="B3956" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Auxílio Financ. - Outorga Créd. Tribut. ICMS - EC nº 123/2022 - Princ. - Etanol - Cota Parte do FUNDEB</t>
+          <t>Dedução Rec. - Auxílio Financ. - Outorga Créd. Tribut. ICMS - EC nº 123/2022 - Princ. - Etanol - Cota Parte dos Municípios</t>
         </is>
       </c>
       <c r="C3956" t="inlineStr">
@@ -67609,29 +67609,29 @@
     <row r="3957">
       <c r="A3957" t="inlineStr">
         <is>
-          <t>9719620000000</t>
+          <t>9719610101003</t>
         </is>
       </c>
       <c r="B3957" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Transferência da Compensação Financeira das Perdas com Arrecadação de ICMS- Art. 3º, §4º, LC 194/2022</t>
+          <t>Dedução Rec. - Auxílio Financ. - Outorga Créd. Tribut. ICMS - EC nº 123/2022 - Princ. - Etanol - Cota Parte do FUNDEB</t>
         </is>
       </c>
       <c r="C3957" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3958">
       <c r="A3958" t="inlineStr">
         <is>
-          <t>9719620100000</t>
+          <t>9719620000000</t>
         </is>
       </c>
       <c r="B3958" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Transf. Compens. Financ. Perdas Arrecad. ICMS -  LC n° 194/2022 - Principal</t>
+          <t>Dedução Rec. - Transferência da Compensação Financeira das Perdas com Arrecadação de ICMS- Art. 3º, §4º, LC 194/2022</t>
         </is>
       </c>
       <c r="C3958" t="inlineStr">
@@ -67643,29 +67643,29 @@
     <row r="3959">
       <c r="A3959" t="inlineStr">
         <is>
-          <t>9719620102000</t>
+          <t>9719620100000</t>
         </is>
       </c>
       <c r="B3959" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Transf. Compens. Financ. Perdas Arrecad. ICMS -  LC n° 194/2022 - Princ. - Cota Parte dos Municípios</t>
+          <t>Dedução Rec. - Transf. Compens. Financ. Perdas Arrecad. ICMS -  LC n° 194/2022 - Principal</t>
         </is>
       </c>
       <c r="C3959" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3960">
       <c r="A3960" t="inlineStr">
         <is>
-          <t>9719620103000</t>
+          <t>9719620102000</t>
         </is>
       </c>
       <c r="B3960" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Transf. Compens. Financ. Perdas Arrecad. ICMS -  LC n° 194/2022 - Princ. - Cota Parte do FUNDEB</t>
+          <t>Dedução Rec. - Transf. Compens. Financ. Perdas Arrecad. ICMS -  LC n° 194/2022 - Princ. - Cota Parte dos Municípios</t>
         </is>
       </c>
       <c r="C3960" t="inlineStr">
@@ -67677,29 +67677,29 @@
     <row r="3961">
       <c r="A3961" t="inlineStr">
         <is>
-          <t>9900000000000</t>
+          <t>9719620103000</t>
         </is>
       </c>
       <c r="B3961" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Outras Receitas Correntes</t>
+          <t>Dedução Rec. - Transf. Compens. Financ. Perdas Arrecad. ICMS -  LC n° 194/2022 - Princ. - Cota Parte do FUNDEB</t>
         </is>
       </c>
       <c r="C3961" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3962">
       <c r="A3962" t="inlineStr">
         <is>
-          <t>9910000000000</t>
+          <t>9900000000000</t>
         </is>
       </c>
       <c r="B3962" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Multas Administrativas, Contratuais e Judiciais</t>
+          <t>Dedução Rec. - Outras Receitas Correntes</t>
         </is>
       </c>
       <c r="C3962" t="inlineStr">
@@ -67711,7 +67711,7 @@
     <row r="3963">
       <c r="A3963" t="inlineStr">
         <is>
-          <t>9911000000000</t>
+          <t>9910000000000</t>
         </is>
       </c>
       <c r="B3963" t="inlineStr">
@@ -67728,12 +67728,12 @@
     <row r="3964">
       <c r="A3964" t="inlineStr">
         <is>
-          <t>9911010000000</t>
+          <t>9911000000000</t>
         </is>
       </c>
       <c r="B3964" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Multas Previstas em Legislação Específica</t>
+          <t>Dedução Rec. - Multas Administrativas, Contratuais e Judiciais</t>
         </is>
       </c>
       <c r="C3964" t="inlineStr">
@@ -67745,12 +67745,12 @@
     <row r="3965">
       <c r="A3965" t="inlineStr">
         <is>
-          <t>9911010100000</t>
+          <t>9911010000000</t>
         </is>
       </c>
       <c r="B3965" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Multas Legisl. Específica - Principal</t>
+          <t>Dedução Rec. - Multas Previstas em Legislação Específica</t>
         </is>
       </c>
       <c r="C3965" t="inlineStr">
@@ -67762,12 +67762,12 @@
     <row r="3966">
       <c r="A3966" t="inlineStr">
         <is>
-          <t>9911010103000</t>
+          <t>9911010100000</t>
         </is>
       </c>
       <c r="B3966" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Multas Legisl. Específica - Princ. - Legislação de Trânsito</t>
+          <t>Dedução Rec. - Multas Legisl. Específica - Principal</t>
         </is>
       </c>
       <c r="C3966" t="inlineStr">
@@ -67779,29 +67779,29 @@
     <row r="3967">
       <c r="A3967" t="inlineStr">
         <is>
-          <t>9911010103003</t>
+          <t>9911010103000</t>
         </is>
       </c>
       <c r="B3967" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Multas Legisl. Específica - Princ. - Legisl. Trânsito - Cota Parte do Fundo Nacional de Segurança e Educação no Trânsito - FUNSET</t>
+          <t>Dedução Rec. - Multas Legisl. Específica - Princ. - Legislação de Trânsito</t>
         </is>
       </c>
       <c r="C3967" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3968">
       <c r="A3968" t="inlineStr">
         <is>
-          <t>9911010103004</t>
+          <t>9911010103003</t>
         </is>
       </c>
       <c r="B3968" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Multas Legisl. Específica - Princ. - Legisl. Trânsito - Cota Parte do Fundo Nacional de Segurança e Educação no Trânsito - FUNSET - Estado</t>
+          <t>Dedução Rec. - Multas Legisl. Específica - Princ. - Legisl. Trânsito - Cota Parte do Fundo Nacional de Segurança e Educação no Trânsito - FUNSET</t>
         </is>
       </c>
       <c r="C3968" t="inlineStr">
@@ -67813,63 +67813,63 @@
     <row r="3969">
       <c r="A3969" t="inlineStr">
         <is>
-          <t>9911010104000</t>
+          <t>9911010103004</t>
         </is>
       </c>
       <c r="B3969" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Multas Legisl. Específica - Princ. - Multa Isolada por Infração a Obrigação Acessória</t>
+          <t>Dedução Rec. - Multas Legisl. Específica - Princ. - Legisl. Trânsito - Cota Parte do Fundo Nacional de Segurança e Educação no Trânsito - FUNSET - Estado</t>
         </is>
       </c>
       <c r="C3969" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3970">
       <c r="A3970" t="inlineStr">
         <is>
-          <t>9911010104001</t>
+          <t>9911010104000</t>
         </is>
       </c>
       <c r="B3970" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Multas Legisl. Específica - Princ. - Multa Isolada Obrig. Acessória - Cessão de Direitos Creditórios - Lei Estadual nº 19.266/10</t>
+          <t>Dedução Rec. - Multas Legisl. Específica - Princ. - Multa Isolada por Infração a Obrigação Acessória</t>
         </is>
       </c>
       <c r="C3970" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3971">
       <c r="A3971" t="inlineStr">
         <is>
-          <t>9911010300000</t>
+          <t>9911010104001</t>
         </is>
       </c>
       <c r="B3971" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Multas Legisl. Específica - Dívida Ativa</t>
+          <t>Dedução Rec. - Multas Legisl. Específica - Princ. - Multa Isolada Obrig. Acessória - Cessão de Direitos Creditórios - Lei Estadual nº 19.266/10</t>
         </is>
       </c>
       <c r="C3971" t="inlineStr">
         <is>
-          <t>Matriz</t>
+          <t>Detalhe</t>
         </is>
       </c>
     </row>
     <row r="3972">
       <c r="A3972" t="inlineStr">
         <is>
-          <t>9911010304000</t>
+          <t>9911010300000</t>
         </is>
       </c>
       <c r="B3972" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Multas Legisl. Específica - DA - Multa Isolada por Infração a Obrigação Acessória</t>
+          <t>Dedução Rec. - Multas Legisl. Específica - Dívida Ativa</t>
         </is>
       </c>
       <c r="C3972" t="inlineStr">
@@ -67881,32 +67881,49 @@
     <row r="3973">
       <c r="A3973" t="inlineStr">
         <is>
-          <t>9911010304001</t>
+          <t>9911010304000</t>
         </is>
       </c>
       <c r="B3973" t="inlineStr">
         <is>
-          <t>Dedução Rec. - Multas Legisl. Específica - DA - Multa Isolada Obrig. Acessória - Cessão de Direitos Creditórios - Lei Estadual nº 19.266/10</t>
+          <t>Dedução Rec. - Multas Legisl. Específica - DA - Multa Isolada por Infração a Obrigação Acessória</t>
         </is>
       </c>
       <c r="C3973" t="inlineStr">
         <is>
-          <t>Detalhe</t>
+          <t>Matriz</t>
         </is>
       </c>
     </row>
     <row r="3974">
       <c r="A3974" t="inlineStr">
         <is>
+          <t>9911010304001</t>
+        </is>
+      </c>
+      <c r="B3974" t="inlineStr">
+        <is>
+          <t>Dedução Rec. - Multas Legisl. Específica - DA - Multa Isolada Obrig. Acessória - Cessão de Direitos Creditórios - Lei Estadual nº 19.266/10</t>
+        </is>
+      </c>
+      <c r="C3974" t="inlineStr">
+        <is>
+          <t>Detalhe</t>
+        </is>
+      </c>
+    </row>
+    <row r="3975">
+      <c r="A3975" t="inlineStr">
+        <is>
           <t>9990000000000</t>
         </is>
       </c>
-      <c r="B3974" t="inlineStr">
+      <c r="B3975" t="inlineStr">
         <is>
           <t>Recursos Arrecadados em Exercícios Anteriores</t>
         </is>
       </c>
-      <c r="C3974" t="inlineStr">
+      <c r="C3975" t="inlineStr">
         <is>
           <t>Matriz</t>
         </is>
@@ -68190,22 +68207,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E629F14D-96BE-4DBD-AECF-F94F71DD701E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE77DA99-642A-4E5A-BDF2-28CAF30A64AB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08A3398D-60B9-4431-B04B-6C5CDFCE995A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95989B48-D08D-434E-8C3B-FBE120D5E0C7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31BD8311-D270-45BC-8BCD-2F9227899AD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB545CC1-B82E-4CAF-A059-024316A862FA}"/>
 </file>